--- a/Data/FlightPlan/FPL_26SEP26.xlsx
+++ b/Data/FlightPlan/FPL_26SEP26.xlsx
@@ -239,6 +239,120 @@
     <t>VN-A521</t>
   </si>
   <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
     <t>16:15</t>
   </si>
   <si>
@@ -251,108 +365,6 @@
     <t>21:05</t>
   </si>
   <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
     <t>VN-A526</t>
   </si>
   <si>
@@ -473,9 +485,6 @@
     <t>11:20</t>
   </si>
   <si>
-    <t>12:35</t>
-  </si>
-  <si>
     <t>18:00</t>
   </si>
   <si>
@@ -659,9 +668,6 @@
     <t>HUI</t>
   </si>
   <si>
-    <t>10:35</t>
-  </si>
-  <si>
     <t>16:00</t>
   </si>
   <si>
@@ -755,9 +761,6 @@
     <t>VN-A632</t>
   </si>
   <si>
-    <t>07:10</t>
-  </si>
-  <si>
     <t>10:15</t>
   </si>
   <si>
@@ -824,9 +827,6 @@
     <t>11:15</t>
   </si>
   <si>
-    <t>13:10</t>
-  </si>
-  <si>
     <t>19:35</t>
   </si>
   <si>
@@ -1217,7 +1217,7 @@
     <t>Total Record(s): 373</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 25, 2026 23:55</t>
+    <t xml:space="preserve">Generated on  Sep 26, 2026 00:27</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2522,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="B32" s="7">
-        <v>148</v>
+        <v>640</v>
       </c>
       <c t="s" r="C32" s="7">
         <v>14</v>
@@ -2538,13 +2538,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2555,7 +2555,7 @@
         <v>13</v>
       </c>
       <c r="B33" s="7">
-        <v>155</v>
+        <v>639</v>
       </c>
       <c t="s" r="C33" s="7">
         <v>14</v>
@@ -2568,32 +2568,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c t="s" r="H33" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
+      <c t="s" r="A34" s="6">
+        <v>13</v>
+      </c>
+      <c r="B34" s="7">
+        <v>644</v>
+      </c>
+      <c t="s" r="C34" s="7">
+        <v>14</v>
+      </c>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
+      <c t="s" r="E34" s="7">
+        <v>75</v>
+      </c>
+      <c r="F34" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G34" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H34" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="I34" s="7">
+        <v>25</v>
+      </c>
+      <c t="s" r="J34" s="7">
+        <v>81</v>
+      </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -2603,23 +2621,23 @@
         <v>13</v>
       </c>
       <c r="B35" s="7">
-        <v>461</v>
+        <v>645</v>
       </c>
       <c t="s" r="C35" s="7">
         <v>14</v>
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c t="s" r="I35" s="7">
         <v>82</v>
@@ -2632,34 +2650,16 @@
       <c r="M35" s="7"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c t="s" r="A36" s="6">
-        <v>13</v>
-      </c>
-      <c r="B36" s="7">
-        <v>462</v>
-      </c>
-      <c t="s" r="C36" s="7">
-        <v>14</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c t="s" r="E36" s="7">
-        <v>80</v>
-      </c>
-      <c r="F36" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G36" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H36" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I36" s="7">
-        <v>42</v>
-      </c>
-      <c t="s" r="J36" s="7">
-        <v>84</v>
-      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
@@ -2669,14 +2669,14 @@
         <v>13</v>
       </c>
       <c r="B37" s="7">
-        <v>515</v>
+        <v>461</v>
       </c>
       <c t="s" r="C37" s="7">
         <v>14</v>
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2688,10 +2688,10 @@
         <v>85</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2702,14 +2702,14 @@
         <v>13</v>
       </c>
       <c r="B38" s="7">
-        <v>508</v>
+        <v>462</v>
       </c>
       <c t="s" r="C38" s="7">
         <v>14</v>
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2721,26 +2721,44 @@
         <v>41</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
+      <c t="s" r="A39" s="6">
+        <v>13</v>
+      </c>
+      <c r="B39" s="7">
+        <v>515</v>
+      </c>
+      <c t="s" r="C39" s="7">
+        <v>14</v>
+      </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
+      <c t="s" r="E39" s="7">
+        <v>84</v>
+      </c>
+      <c r="F39" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G39" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H39" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="I39" s="7">
+        <v>64</v>
+      </c>
+      <c t="s" r="J39" s="7">
+        <v>51</v>
+      </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
@@ -2750,63 +2768,45 @@
         <v>13</v>
       </c>
       <c r="B40" s="7">
-        <v>212</v>
+        <v>508</v>
       </c>
       <c t="s" r="C40" s="7">
         <v>14</v>
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c t="s" r="H40" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I40" s="7">
         <v>89</v>
       </c>
-      <c t="s" r="I40" s="7">
+      <c t="s" r="J40" s="7">
         <v>90</v>
-      </c>
-      <c t="s" r="J40" s="7">
-        <v>91</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c t="s" r="A41" s="6">
-        <v>13</v>
-      </c>
-      <c r="B41" s="7">
-        <v>215</v>
-      </c>
-      <c t="s" r="C41" s="7">
-        <v>14</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c t="s" r="E41" s="7">
-        <v>88</v>
-      </c>
-      <c r="F41" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G41" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="H41" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I41" s="7">
-        <v>92</v>
-      </c>
-      <c t="s" r="J41" s="7">
-        <v>64</v>
-      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
@@ -2816,14 +2816,14 @@
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>807</v>
+        <v>212</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2832,10 +2832,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H42" s="8">
+        <v>92</v>
+      </c>
+      <c t="s" r="I42" s="7">
         <v>93</v>
-      </c>
-      <c t="s" r="I42" s="7">
-        <v>66</v>
       </c>
       <c t="s" r="J42" s="7">
         <v>94</v>
@@ -2849,20 +2849,20 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>800</v>
+        <v>215</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>20</v>
@@ -2871,7 +2871,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2882,14 +2882,14 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c t="s" r="C44" s="7">
         <v>14</v>
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -2898,29 +2898,47 @@
         <v>20</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c t="s" r="I44" s="7">
+        <v>66</v>
+      </c>
+      <c t="s" r="J44" s="7">
         <v>97</v>
-      </c>
-      <c t="s" r="J44" s="7">
-        <v>90</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
+      <c t="s" r="A45" s="6">
+        <v>13</v>
+      </c>
+      <c r="B45" s="7">
+        <v>800</v>
+      </c>
+      <c t="s" r="C45" s="7">
+        <v>14</v>
+      </c>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
+      <c t="s" r="E45" s="7">
+        <v>91</v>
+      </c>
+      <c r="F45" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G45" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H45" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I45" s="7">
+        <v>98</v>
+      </c>
+      <c t="s" r="J45" s="7">
+        <v>99</v>
+      </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
@@ -2930,14 +2948,14 @@
         <v>13</v>
       </c>
       <c r="B46" s="7">
-        <v>392</v>
+        <v>822</v>
       </c>
       <c t="s" r="C46" s="7">
         <v>14</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2946,47 +2964,29 @@
         <v>20</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c t="s" r="A47" s="6">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7">
-        <v>393</v>
-      </c>
-      <c t="s" r="C47" s="7">
-        <v>14</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c t="s" r="E47" s="7">
-        <v>98</v>
-      </c>
-      <c r="F47" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G47" s="8">
-        <v>99</v>
-      </c>
-      <c t="s" r="H47" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I47" s="7">
-        <v>102</v>
-      </c>
-      <c t="s" r="J47" s="7">
-        <v>42</v>
-      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
@@ -2996,14 +2996,14 @@
         <v>13</v>
       </c>
       <c r="B48" s="7">
-        <v>274</v>
+        <v>392</v>
       </c>
       <c t="s" r="C48" s="7">
         <v>14</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3012,64 +3012,72 @@
         <v>20</v>
       </c>
       <c t="s" r="H48" s="8">
+        <v>102</v>
+      </c>
+      <c t="s" r="I48" s="7">
         <v>103</v>
       </c>
-      <c t="s" r="I48" s="7">
+      <c t="s" r="J48" s="7">
         <v>104</v>
       </c>
-      <c t="s" r="J48" s="7">
+      <c t="s" r="K48" s="7">
         <v>105</v>
       </c>
-      <c r="K48" s="7"/>
       <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c t="s" r="M48" s="7">
+        <v>106</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c t="s" r="A49" s="6">
         <v>13</v>
       </c>
       <c r="B49" s="7">
-        <v>275</v>
+        <v>393</v>
       </c>
       <c t="s" r="C49" s="7">
         <v>14</v>
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>106</v>
-      </c>
-      <c r="K49" s="7"/>
+        <v>42</v>
+      </c>
+      <c t="s" r="K49" s="7">
+        <v>61</v>
+      </c>
       <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
+      <c t="s" r="M49" s="7">
+        <v>107</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c t="s" r="A50" s="6">
         <v>13</v>
       </c>
       <c r="B50" s="7">
-        <v>640</v>
+        <v>274</v>
       </c>
       <c t="s" r="C50" s="7">
         <v>14</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3078,64 +3086,72 @@
         <v>20</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c t="s" r="I50" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>108</v>
-      </c>
-      <c r="K50" s="7"/>
+        <v>109</v>
+      </c>
+      <c t="s" r="K50" s="7">
+        <v>110</v>
+      </c>
       <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
+      <c t="s" r="M50" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c t="s" r="A51" s="6">
         <v>13</v>
       </c>
       <c r="B51" s="7">
-        <v>639</v>
+        <v>275</v>
       </c>
       <c t="s" r="C51" s="7">
         <v>14</v>
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>110</v>
-      </c>
-      <c r="K51" s="7"/>
+        <v>112</v>
+      </c>
+      <c t="s" r="K51" s="7">
+        <v>113</v>
+      </c>
       <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
+      <c t="s" r="M51" s="7">
+        <v>77</v>
+      </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c t="s" r="A52" s="6">
         <v>13</v>
       </c>
       <c r="B52" s="7">
-        <v>644</v>
+        <v>148</v>
       </c>
       <c t="s" r="C52" s="7">
         <v>14</v>
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3144,13 +3160,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3161,29 +3177,29 @@
         <v>13</v>
       </c>
       <c r="B53" s="7">
-        <v>645</v>
+        <v>155</v>
       </c>
       <c t="s" r="C53" s="7">
         <v>14</v>
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3216,7 +3232,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3225,10 +3241,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>61</v>
@@ -3249,22 +3265,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3282,7 +3298,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3291,7 +3307,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I57" s="7">
         <v>60</v>
@@ -3315,13 +3331,13 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>41</v>
@@ -3348,7 +3364,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3357,13 +3373,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3377,26 +3393,26 @@
         <v>7660</v>
       </c>
       <c t="s" r="C60" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3410,11 +3426,11 @@
         <v>7660</v>
       </c>
       <c t="s" r="C61" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3423,13 +3439,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3462,7 +3478,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3474,10 +3490,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3495,7 +3511,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3507,10 +3523,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3528,7 +3544,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3540,10 +3556,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3561,7 +3577,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3573,10 +3589,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3609,7 +3625,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3618,13 +3634,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3642,19 +3658,19 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>30</v>
@@ -3675,22 +3691,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3708,13 +3724,13 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>20</v>
@@ -3723,7 +3739,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3741,7 +3757,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3750,13 +3766,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3774,22 +3790,22 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3807,7 +3823,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3819,10 +3835,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3840,7 +3856,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3852,10 +3868,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3888,22 +3904,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3921,7 +3937,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3930,10 +3946,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>61</v>
@@ -3954,22 +3970,22 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I79" s="7">
         <v>42</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3987,22 +4003,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4020,13 +4036,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>20</v>
@@ -4035,7 +4051,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4068,22 +4084,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4101,7 +4117,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4110,13 +4126,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4134,22 +4150,22 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4167,7 +4183,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4176,13 +4192,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4215,7 +4231,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4224,13 +4240,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4248,19 +4264,19 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>62</v>
@@ -4281,7 +4297,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4290,13 +4306,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4329,22 +4345,22 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4362,7 +4378,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4371,7 +4387,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>52</v>
@@ -4395,13 +4411,13 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>20</v>
@@ -4410,7 +4426,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4428,7 +4444,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4437,13 +4453,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4461,13 +4477,13 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>20</v>
@@ -4476,7 +4492,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4509,7 +4525,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4518,10 +4534,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>42</v>
@@ -4542,22 +4558,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4575,7 +4591,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4590,7 +4606,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4608,7 +4624,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4620,10 +4636,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4656,7 +4672,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4668,7 +4684,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>19</v>
@@ -4689,7 +4705,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4698,7 +4714,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="I104" s="7">
         <v>31</v>
@@ -4722,19 +4738,19 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>56</v>
@@ -4770,7 +4786,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4782,10 +4798,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4803,7 +4819,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4812,13 +4828,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4836,19 +4852,19 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>51</v>
@@ -4869,7 +4885,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4881,7 +4897,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>65</v>
@@ -4902,7 +4918,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4914,10 +4930,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4935,7 +4951,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4944,13 +4960,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4968,22 +4984,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5012,26 +5028,26 @@
         <v>7707</v>
       </c>
       <c t="s" r="C115" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5045,11 +5061,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C116" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5061,7 +5077,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>52</v>
@@ -5082,7 +5098,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5097,7 +5113,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5115,7 +5131,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5127,10 +5143,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5163,7 +5179,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5175,7 +5191,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>19</v>
@@ -5196,7 +5212,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5205,7 +5221,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>31</v>
@@ -5229,19 +5245,19 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>35</v>
@@ -5262,7 +5278,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5274,10 +5290,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5310,7 +5326,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5319,13 +5335,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5343,22 +5359,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5376,7 +5392,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5385,13 +5401,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5409,13 +5425,13 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>41</v>
@@ -5424,7 +5440,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5457,7 +5473,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5469,10 +5485,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5490,7 +5506,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5502,10 +5518,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5523,7 +5539,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5532,13 +5548,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5556,22 +5572,22 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5589,7 +5605,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5598,13 +5614,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5633,11 +5649,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C136" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5649,17 +5665,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="K136" s="7">
         <v>49</v>
       </c>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -5670,11 +5686,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5686,10 +5702,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5703,11 +5719,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5716,13 +5732,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5736,26 +5752,26 @@
         <v>7621</v>
       </c>
       <c t="s" r="C139" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5788,7 +5804,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5797,13 +5813,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5821,19 +5837,19 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>61</v>
@@ -5854,7 +5870,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5863,13 +5879,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5887,22 +5903,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5920,7 +5936,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5932,7 +5948,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>24</v>
@@ -5953,7 +5969,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5965,10 +5981,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5986,7 +6002,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5995,10 +6011,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>61</v>
@@ -6034,7 +6050,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6046,10 +6062,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6067,7 +6083,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6079,10 +6095,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6100,7 +6116,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6112,10 +6128,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6133,7 +6149,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6148,7 +6164,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6166,7 +6182,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6175,13 +6191,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6214,7 +6230,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6229,7 +6245,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6247,7 +6263,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6259,10 +6275,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6280,7 +6296,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6292,7 +6308,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>70</v>
@@ -6328,22 +6344,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6361,7 +6377,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6373,7 +6389,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>25</v>
@@ -6394,7 +6410,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6406,10 +6422,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6427,7 +6443,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6436,13 +6452,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6475,7 +6491,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6487,10 +6503,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6508,7 +6524,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6520,7 +6536,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>45</v>
@@ -6541,7 +6557,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6550,13 +6566,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6574,19 +6590,19 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>27</v>
@@ -6607,7 +6623,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6622,7 +6638,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6655,7 +6671,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6664,13 +6680,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6688,13 +6704,13 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>53</v>
@@ -6703,7 +6719,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6721,7 +6737,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6730,13 +6746,13 @@
         <v>53</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6754,19 +6770,19 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>56</v>
@@ -6787,7 +6803,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6796,13 +6812,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6820,22 +6836,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6868,7 +6884,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6880,10 +6896,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6901,7 +6917,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6913,10 +6929,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6934,7 +6950,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6943,10 +6959,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>51</v>
@@ -6956,7 +6972,7 @@
       </c>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -6971,29 +6987,29 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="K180" s="7">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7008,7 +7024,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7020,10 +7036,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7041,7 +7057,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7053,10 +7069,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7089,7 +7105,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7098,10 +7114,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>61</v>
@@ -7122,22 +7138,22 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7155,19 +7171,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>43</v>
@@ -7188,13 +7204,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>41</v>
@@ -7203,7 +7219,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7221,7 +7237,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7230,13 +7246,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7254,13 +7270,13 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>41</v>
@@ -7269,7 +7285,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7287,7 +7303,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7296,13 +7312,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7320,22 +7336,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7368,7 +7384,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7377,10 +7393,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>74</v>
@@ -7401,19 +7417,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>30</v>
@@ -7434,7 +7450,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7443,13 +7459,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>42</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7467,13 +7483,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>20</v>
@@ -7482,7 +7498,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7500,7 +7516,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7509,13 +7525,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7533,22 +7549,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7581,7 +7597,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7590,13 +7606,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7614,22 +7630,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7647,7 +7663,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7656,13 +7672,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7680,13 +7696,13 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>20</v>
@@ -7695,7 +7711,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7728,7 +7744,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7737,13 +7753,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7761,22 +7777,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7794,22 +7810,22 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>53</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7827,7 +7843,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7836,13 +7852,13 @@
         <v>53</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7860,13 +7876,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>41</v>
@@ -7875,7 +7891,7 @@
         <v>272</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7893,7 +7909,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7908,7 +7924,7 @@
         <v>273</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7950,10 +7966,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>59</v>
@@ -7980,7 +7996,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>41</v>
@@ -7989,7 +8005,7 @@
         <v>275</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8016,7 +8032,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I214" s="7">
         <v>276</v>
@@ -8046,16 +8062,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8082,10 +8098,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>52</v>
@@ -8112,16 +8128,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8187,7 +8203,7 @@
         <v>278</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8232,10 +8248,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8265,10 +8281,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8295,10 +8311,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>280</v>
@@ -8325,13 +8341,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>281</v>
@@ -8382,7 +8398,7 @@
         <v>283</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8409,10 +8425,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>62</v>
@@ -8439,16 +8455,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8475,13 +8491,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8505,13 +8521,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>26</v>
@@ -8559,17 +8575,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8596,10 +8612,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8629,10 +8645,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8662,10 +8678,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8707,10 +8723,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>30</v>
@@ -8737,16 +8753,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8776,7 +8792,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>287</v>
@@ -8812,7 +8828,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8839,10 +8855,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>288</v>
@@ -8869,13 +8885,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>277</v>
@@ -8923,10 +8939,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8953,13 +8969,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8983,7 +8999,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>41</v>
@@ -9022,7 +9038,7 @@
         <v>292</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>293</v>
@@ -9055,7 +9071,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>294</v>
@@ -9166,7 +9182,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>297</v>
@@ -9196,16 +9212,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9238,7 +9254,7 @@
         <v>299</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9268,7 +9284,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>25</v>
@@ -9349,10 +9365,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9379,13 +9395,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>287</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9409,16 +9425,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9460,13 +9476,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9490,7 +9506,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>303</v>
@@ -9499,7 +9515,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9526,7 +9542,7 @@
         <v>303</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>65</v>
@@ -9546,7 +9562,7 @@
         <v>8020</v>
       </c>
       <c t="s" r="C265" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
@@ -9556,13 +9572,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>304</v>
@@ -9579,7 +9595,7 @@
         <v>8021</v>
       </c>
       <c t="s" r="C266" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
@@ -9589,10 +9605,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>305</v>
@@ -9640,7 +9656,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>308</v>
@@ -9670,16 +9686,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9706,13 +9722,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9736,13 +9752,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>67</v>
@@ -9775,10 +9791,10 @@
         <v>310</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9859,7 +9875,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9892,7 +9908,7 @@
         <v>315</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9919,13 +9935,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9949,7 +9965,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>41</v>
@@ -9958,7 +9974,7 @@
         <v>316</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9985,13 +10001,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10015,7 +10031,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>53</v>
@@ -10024,7 +10040,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10051,10 +10067,10 @@
         <v>53</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>277</v>
@@ -10099,13 +10115,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10129,7 +10145,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>20</v>
@@ -10138,7 +10154,7 @@
         <v>316</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10168,10 +10184,10 @@
         <v>318</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10282,10 +10298,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10312,10 +10328,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>50</v>
@@ -10342,16 +10358,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10381,7 +10397,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>69</v>
@@ -10414,10 +10430,10 @@
         <v>323</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10447,7 +10463,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>70</v>
@@ -10495,17 +10511,17 @@
         <v>20</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="K296" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10532,7 +10548,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>21</v>
@@ -10565,10 +10581,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10598,10 +10614,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10646,10 +10662,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10679,10 +10695,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10712,7 +10728,7 @@
         <v>326</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>73</v>
@@ -10748,7 +10764,7 @@
         <v>273</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10787,13 +10803,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>297</v>
@@ -10820,16 +10836,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>328</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10853,10 +10869,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="H308" s="8">
         <v>85</v>
-      </c>
-      <c t="s" r="H308" s="8">
-        <v>81</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>51</v>
@@ -10886,13 +10902,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>330</v>
@@ -10919,13 +10935,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>303</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>331</v>
@@ -10955,7 +10971,7 @@
         <v>303</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>332</v>
@@ -10985,16 +11001,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11042,7 +11058,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11072,10 +11088,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11108,14 +11124,14 @@
         <v>315</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11142,7 +11158,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>51</v>
@@ -11152,7 +11168,7 @@
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11194,7 +11210,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>322</v>
@@ -11227,7 +11243,7 @@
         <v>298</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>49</v>
@@ -11296,7 +11312,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11329,7 +11345,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11443,7 +11459,7 @@
         <v>342</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11470,13 +11486,13 @@
         <v>53</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="I328" s="7">
         <v>308</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11500,13 +11516,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>53</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>45</v>
@@ -11539,7 +11555,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>293</v>
@@ -11584,13 +11600,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11614,16 +11630,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11650,7 +11666,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>276</v>
@@ -11680,7 +11696,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>20</v>
@@ -11716,7 +11732,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>46</v>
@@ -11746,7 +11762,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>55</v>
@@ -11836,7 +11852,7 @@
         <v>276</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11866,10 +11882,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11899,10 +11915,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11932,10 +11948,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11965,7 +11981,7 @@
         <v>350</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>351</v>
@@ -12049,7 +12065,7 @@
         <v>315</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12079,10 +12095,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12109,13 +12125,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>288</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12139,7 +12155,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>41</v>
@@ -12148,7 +12164,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12178,10 +12194,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12220,7 +12236,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>20</v>
@@ -12229,7 +12245,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12256,10 +12272,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>65</v>
@@ -12286,7 +12302,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>20</v>
@@ -12295,7 +12311,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12325,10 +12341,10 @@
         <v>356</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12358,10 +12374,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12409,7 +12425,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12469,10 +12485,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>65</v>
@@ -12499,7 +12515,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>41</v>
@@ -12508,7 +12524,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12538,7 +12554,7 @@
         <v>326</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>358</v>
@@ -12571,7 +12587,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>359</v>
@@ -12652,10 +12668,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12685,7 +12701,7 @@
         <v>362</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>330</v>
@@ -12718,10 +12734,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12796,7 +12812,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>38</v>
@@ -12826,16 +12842,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12859,16 +12875,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12892,13 +12908,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>22</v>
@@ -12925,16 +12941,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12958,7 +12974,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>20</v>
@@ -12967,7 +12983,7 @@
         <v>365</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13009,13 +13025,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13039,13 +13055,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>65</v>
@@ -13075,13 +13091,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>330</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13105,7 +13121,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>41</v>
@@ -13114,7 +13130,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13147,7 +13163,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13186,7 +13202,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>53</v>
@@ -13195,7 +13211,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13222,13 +13238,13 @@
         <v>53</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13252,13 +13268,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>67</v>
@@ -13285,7 +13301,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>20</v>
@@ -13294,7 +13310,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13321,7 +13337,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>368</v>
@@ -13351,7 +13367,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>55</v>
@@ -13360,7 +13376,7 @@
         <v>369</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13405,10 +13421,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13438,10 +13454,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13471,10 +13487,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13504,7 +13520,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>280</v>
@@ -13540,7 +13556,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13585,10 +13601,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13618,7 +13634,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>372</v>
@@ -13651,10 +13667,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13681,13 +13697,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13711,16 +13727,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13750,7 +13766,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>293</v>
@@ -13795,13 +13811,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>353</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13846,10 +13862,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13879,10 +13895,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13912,10 +13928,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13954,16 +13970,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14026,7 +14042,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>26</v>
@@ -14059,10 +14075,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14104,13 +14120,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>361</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14134,16 +14150,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14173,10 +14189,10 @@
         <v>377</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14206,10 +14222,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14242,7 +14258,7 @@
         <v>368</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14320,10 +14336,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14356,7 +14372,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14383,13 +14399,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14413,13 +14429,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>64</v>
@@ -14452,7 +14468,7 @@
         <v>323</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>382</v>
@@ -14485,7 +14501,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>291</v>
@@ -14515,13 +14531,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14545,13 +14561,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>365</v>
@@ -14599,7 +14615,7 @@
         <v>384</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>277</v>
@@ -14635,7 +14651,7 @@
         <v>385</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14761,10 +14777,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14791,13 +14807,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14811,7 +14827,7 @@
         <v>8912</v>
       </c>
       <c t="s" r="C440" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
@@ -14821,13 +14837,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>389</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>311</v>
@@ -14844,7 +14860,7 @@
         <v>2867</v>
       </c>
       <c t="s" r="C441" s="7">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
@@ -14860,10 +14876,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14902,13 +14918,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>391</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>345</v>
@@ -14989,17 +15005,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="K446" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15023,13 +15039,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I447" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15071,13 +15087,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15101,7 +15117,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>397</v>
@@ -15110,7 +15126,7 @@
         <v>392</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15137,13 +15153,13 @@
         <v>397</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15188,10 +15204,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15221,7 +15237,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>399</v>
@@ -15254,10 +15270,10 @@
         <v>400</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>

--- a/Data/FlightPlan/FPL_26SEP26.xlsx
+++ b/Data/FlightPlan/FPL_26SEP26.xlsx
@@ -344,6 +344,9 @@
     <t>13:00</t>
   </si>
   <si>
+    <t>12:57</t>
+  </si>
+  <si>
     <t>THD</t>
   </si>
   <si>
@@ -380,6 +383,12 @@
     <t>11:04</t>
   </si>
   <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
     <t>17:45</t>
   </si>
   <si>
@@ -458,6 +467,9 @@
     <t>12:35</t>
   </si>
   <si>
+    <t>13:01</t>
+  </si>
+  <si>
     <t>18:00</t>
   </si>
   <si>
@@ -518,684 +530,705 @@
     <t>10:00</t>
   </si>
   <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:47</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>WUX</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>13:31</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
     <t>12:45</t>
   </si>
   <si>
-    <t>14:30</t>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>771A *</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:42</t>
+  </si>
+  <si>
+    <t>09:46</t>
   </si>
   <si>
     <t>15:10</t>
   </si>
   <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>08:22</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
     <t>17:05</t>
   </si>
   <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:47</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>WUX</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>10:48</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:11</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:12</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>11:13</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>08:33</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>13:31</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>12:38</t>
-  </si>
-  <si>
-    <t>771A *</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>11:51</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:42</t>
-  </si>
-  <si>
-    <t>09:46</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:43</t>
-  </si>
-  <si>
-    <t>08:22</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>09:44</t>
-  </si>
-  <si>
-    <t>11:11</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
     <t>20:40</t>
   </si>
   <si>
@@ -1313,9 +1346,6 @@
     <t>09:04</t>
   </si>
   <si>
-    <t>15:02</t>
-  </si>
-  <si>
     <t>02:15</t>
   </si>
   <si>
@@ -1331,9 +1361,6 @@
     <t>10:08</t>
   </si>
   <si>
-    <t>11:57</t>
-  </si>
-  <si>
     <t>14:15</t>
   </si>
   <si>
@@ -1364,9 +1391,6 @@
     <t>13:44</t>
   </si>
   <si>
-    <t>15:20</t>
-  </si>
-  <si>
     <t>05:45</t>
   </si>
   <si>
@@ -1376,12 +1400,15 @@
     <t>VN-A816</t>
   </si>
   <si>
-    <t>20:44</t>
+    <t>20:47</t>
   </si>
   <si>
     <t>VN-A817</t>
   </si>
   <si>
+    <t>13:09</t>
+  </si>
+  <si>
     <t>NQZ</t>
   </si>
   <si>
@@ -1397,7 +1424,7 @@
     <t>Total Record(s): 372</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 26, 2026 10:49</t>
+    <t xml:space="preserve">Generated on  Sep 26, 2026 12:05</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3120,7 +3147,9 @@
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
+      <c t="s" r="M44" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c t="s" r="A45" s="6">
@@ -3143,10 +3172,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J45" s="7">
         <v>89</v>
@@ -3173,16 +3202,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3212,10 +3241,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3245,7 +3274,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J48" s="7">
         <v>101</v>
@@ -3281,7 +3310,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3293,7 +3322,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J50" s="7">
         <v>62</v>
@@ -3301,7 +3330,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c t="s" r="M50" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -3316,7 +3345,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3328,7 +3357,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>108</v>
@@ -3336,7 +3365,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3351,7 +3380,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3370,7 +3399,9 @@
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
+      <c t="s" r="M52" s="7">
+        <v>124</v>
+      </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c t="s" r="A53" s="6">
@@ -3384,7 +3415,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3401,9 +3432,13 @@
       <c t="s" r="J53" s="7">
         <v>29</v>
       </c>
-      <c r="K53" s="7"/>
+      <c t="s" r="K53" s="7">
+        <v>52</v>
+      </c>
       <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
+      <c t="s" r="M53" s="7">
+        <v>125</v>
+      </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c t="s" r="A54" s="6">
@@ -3417,7 +3452,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3429,10 +3464,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3446,11 +3481,11 @@
         <v>7660</v>
       </c>
       <c t="s" r="C55" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3462,10 +3497,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3479,11 +3514,11 @@
         <v>7660</v>
       </c>
       <c t="s" r="C56" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3492,13 +3527,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3531,7 +3566,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3546,12 +3581,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3566,7 +3601,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3578,10 +3613,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3599,7 +3634,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3611,10 +3646,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3632,7 +3667,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3644,10 +3679,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3680,7 +3715,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3695,12 +3730,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -3715,7 +3750,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3727,7 +3762,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>62</v>
@@ -3735,7 +3770,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3750,7 +3785,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3759,18 +3794,18 @@
         <v>83</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I65" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3785,26 +3820,28 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
+      <c t="s" r="M66" s="7">
+        <v>152</v>
+      </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c t="s" r="A67" s="6">
@@ -3818,7 +3855,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3833,7 +3870,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3866,27 +3903,27 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -3901,7 +3938,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3910,13 +3947,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3934,22 +3971,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3967,7 +4004,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3976,13 +4013,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4015,7 +4052,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4024,20 +4061,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="K74" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4052,29 +4089,29 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>40</v>
       </c>
       <c t="s" r="K75" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4089,7 +4126,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4098,20 +4135,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>63</v>
       </c>
       <c t="s" r="K76" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>169</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4126,13 +4163,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>25</v>
@@ -4141,14 +4178,14 @@
         <v>50</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="K77" s="7">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>171</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4163,7 +4200,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4181,11 +4218,11 @@
         <v>88</v>
       </c>
       <c t="s" r="K78" s="7">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>172</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4215,7 +4252,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4227,10 +4264,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4248,7 +4285,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4257,7 +4294,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I81" s="7">
         <v>53</v>
@@ -4281,13 +4318,13 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>25</v>
@@ -4314,7 +4351,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4347,7 +4384,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4711,14 +4748,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>196</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
+      <c t="s" r="M96" s="7">
+        <v>197</v>
+      </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c t="s" r="A97" s="6">
@@ -4747,7 +4786,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4777,10 +4816,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4807,7 +4846,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>175</v>
@@ -4837,7 +4876,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>25</v>
@@ -4846,7 +4885,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4875,31 +4914,31 @@
         <v>7707</v>
       </c>
       <c t="s" r="C102" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -4910,11 +4949,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C103" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4926,7 +4965,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>53</v>
@@ -4947,7 +4986,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4962,7 +5001,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4980,7 +5019,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4992,10 +5031,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5028,7 +5067,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5040,7 +5079,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>19</v>
@@ -5061,7 +5100,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5070,7 +5109,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>29</v>
@@ -5094,13 +5133,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
@@ -5127,7 +5166,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5139,7 +5178,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>93</v>
@@ -5175,7 +5214,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5184,18 +5223,18 @@
         <v>39</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5210,22 +5249,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5243,7 +5282,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5252,7 +5291,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>32</v>
@@ -5276,13 +5315,13 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>39</v>
@@ -5291,7 +5330,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5324,7 +5363,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5336,15 +5375,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5359,7 +5398,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5371,17 +5410,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>221</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5396,7 +5435,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5405,13 +5444,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5429,22 +5468,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5462,7 +5501,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5471,7 +5510,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>222</v>
@@ -5506,7 +5545,7 @@
         <v>5069</v>
       </c>
       <c t="s" r="C123" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
@@ -5532,7 +5571,7 @@
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5543,7 +5582,7 @@
         <v>7620</v>
       </c>
       <c t="s" r="C124" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
@@ -5576,7 +5615,7 @@
         <v>7620</v>
       </c>
       <c t="s" r="C125" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
@@ -5595,7 +5634,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5609,7 +5648,7 @@
         <v>7621</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
@@ -5673,10 +5712,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5708,7 +5747,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>62</v>
@@ -5743,7 +5782,7 @@
         <v>231</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>232</v>
@@ -5781,11 +5820,13 @@
         <v>187</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
-      <c r="M131" s="7"/>
+      <c t="s" r="M131" s="7">
+        <v>234</v>
+      </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c t="s" r="A132" s="6">
@@ -5811,7 +5852,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>175</v>
@@ -5844,10 +5885,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5874,10 +5915,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>62</v>
@@ -5913,7 +5954,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5925,7 +5966,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>182</v>
@@ -5948,7 +5989,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5963,7 +6004,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5981,7 +6022,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5996,7 +6037,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6014,7 +6055,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6026,7 +6067,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>72</v>
@@ -6047,7 +6088,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6056,13 +6097,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6095,7 +6136,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6104,10 +6145,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>40</v>
@@ -6115,7 +6156,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6130,19 +6171,19 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>63</v>
@@ -6150,7 +6191,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6165,7 +6206,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6174,13 +6215,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6198,13 +6239,13 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>25</v>
@@ -6213,7 +6254,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6231,7 +6272,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6243,10 +6284,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6264,7 +6305,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6276,10 +6317,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6312,13 +6353,13 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>25</v>
@@ -6327,12 +6368,12 @@
         <v>232</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6347,7 +6388,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6359,7 +6400,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>56</v>
@@ -6380,7 +6421,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6392,10 +6433,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6413,7 +6454,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6422,7 +6463,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>222</v>
@@ -6461,7 +6502,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6476,12 +6517,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6496,7 +6537,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6508,7 +6549,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>44</v>
@@ -6529,7 +6570,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6541,10 +6582,10 @@
         <v>231</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6562,7 +6603,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6574,10 +6615,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6595,7 +6636,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6610,7 +6651,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6643,7 +6684,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6652,13 +6693,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6678,13 +6719,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>54</v>
@@ -6700,7 +6741,7 @@
       </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6715,7 +6756,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6724,13 +6765,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6748,13 +6789,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>25</v>
@@ -6781,7 +6822,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6790,13 +6831,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6814,22 +6855,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6862,7 +6903,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6877,7 +6918,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6897,7 +6938,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6912,12 +6953,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6932,7 +6973,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6941,20 +6982,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I169" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="K169" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>153</v>
+        <v>52</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6969,29 +7010,29 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>52</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>87</v>
+        <v>137</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7006,7 +7047,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7015,7 +7056,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>277</v>
@@ -7039,13 +7080,13 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>25</v>
@@ -7054,7 +7095,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7099,7 +7140,7 @@
         <v>281</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>62</v>
@@ -7134,10 +7175,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7169,14 +7210,16 @@
         <v>281</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>41</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>283</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c t="s" r="A177" s="6">
@@ -7235,7 +7278,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>189</v>
@@ -7271,7 +7314,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7304,7 +7347,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7316,7 +7359,7 @@
         <v>231</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>74</v>
@@ -7324,7 +7367,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7339,7 +7382,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7351,7 +7394,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>27</v>
@@ -7359,7 +7402,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7374,7 +7417,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7383,18 +7426,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7409,13 +7452,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>25</v>
@@ -7442,7 +7485,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7451,10 +7494,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>100</v>
@@ -7475,22 +7518,22 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7523,7 +7566,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7535,15 +7578,15 @@
         <v>83</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7558,7 +7601,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7573,7 +7616,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7593,7 +7636,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7602,16 +7645,16 @@
         <v>25</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>169</v>
+        <v>297</v>
       </c>
       <c t="s" r="K190" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
@@ -7630,13 +7673,13 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>25</v>
@@ -7645,10 +7688,10 @@
         <v>42</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="K191" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
@@ -7667,7 +7710,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7676,13 +7719,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>183</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7700,22 +7743,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7748,7 +7791,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7757,13 +7800,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7783,27 +7826,27 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>303</v>
+        <v>42</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7818,7 +7861,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7830,10 +7873,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7851,7 +7894,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7863,7 +7906,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>277</v>
@@ -7884,7 +7927,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7896,10 +7939,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7917,7 +7960,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7929,10 +7972,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7965,7 +8008,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7985,7 +8028,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8000,7 +8043,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8012,15 +8055,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8035,7 +8078,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8047,14 +8090,16 @@
         <v>105</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>196</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
-      <c r="M204" s="7"/>
+      <c t="s" r="M204" s="7">
+        <v>157</v>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c t="s" r="A205" s="6">
@@ -8068,7 +8113,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8080,14 +8125,18 @@
         <v>39</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>169</v>
+        <v>297</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>170</v>
-      </c>
-      <c r="K205" s="7"/>
+        <v>173</v>
+      </c>
+      <c t="s" r="K205" s="7">
+        <v>225</v>
+      </c>
       <c r="L205" s="7"/>
-      <c r="M205" s="7"/>
+      <c t="s" r="M205" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
@@ -8101,7 +8150,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8134,7 +8183,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8146,7 +8195,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>46</v>
@@ -8167,7 +8216,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8176,13 +8225,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8200,22 +8249,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8248,7 +8297,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8260,10 +8309,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8281,7 +8330,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8314,7 +8363,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8326,10 +8375,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8347,7 +8396,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8362,7 +8411,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8395,7 +8444,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8407,7 +8456,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>78</v>
@@ -8430,7 +8479,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8450,7 +8499,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>321</v>
+        <v>151</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8465,7 +8514,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8477,14 +8526,18 @@
         <v>39</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>169</v>
+        <v>297</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>88</v>
       </c>
-      <c r="K218" s="7"/>
+      <c t="s" r="K218" s="7">
+        <v>41</v>
+      </c>
       <c r="L218" s="7"/>
-      <c r="M218" s="7"/>
+      <c t="s" r="M218" s="7">
+        <v>98</v>
+      </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c t="s" r="A219" s="6">
@@ -8498,7 +8551,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8507,7 +8560,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>226</v>
@@ -8515,9 +8568,13 @@
       <c t="s" r="J219" s="7">
         <v>53</v>
       </c>
-      <c r="K219" s="7"/>
+      <c t="s" r="K219" s="7">
+        <v>322</v>
+      </c>
       <c r="L219" s="7"/>
-      <c r="M219" s="7"/>
+      <c t="s" r="M219" s="7">
+        <v>284</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c t="s" r="A220" s="6">
@@ -8531,22 +8588,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8572,14 +8629,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B222" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8591,17 +8648,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="K222" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8616,7 +8673,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8628,14 +8685,16 @@
         <v>39</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
@@ -8649,7 +8708,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8664,11 +8723,15 @@
         <v>86</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>324</v>
-      </c>
-      <c r="K224" s="7"/>
+        <v>326</v>
+      </c>
+      <c t="s" r="K224" s="7">
+        <v>88</v>
+      </c>
       <c r="L224" s="7"/>
-      <c r="M224" s="7"/>
+      <c t="s" r="M224" s="7">
+        <v>199</v>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c t="s" r="A225" s="6">
@@ -8682,7 +8745,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8694,14 +8757,18 @@
         <v>39</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>325</v>
-      </c>
-      <c r="K225" s="7"/>
+        <v>327</v>
+      </c>
+      <c t="s" r="K225" s="7">
+        <v>67</v>
+      </c>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>189</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c r="A226" s="6"/>
@@ -8730,7 +8797,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8739,10 +8806,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>27</v>
@@ -8750,7 +8817,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8765,13 +8832,13 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>39</v>
@@ -8780,12 +8847,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8800,7 +8867,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8812,14 +8879,16 @@
         <v>54</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
-      <c r="M229" s="7"/>
+      <c t="s" r="M229" s="7">
+        <v>330</v>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1">
       <c t="s" r="A230" s="6">
@@ -8833,7 +8902,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8848,7 +8917,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8866,7 +8935,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8881,7 +8950,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8899,7 +8968,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8911,10 +8980,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8947,13 +9016,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>39</v>
@@ -8962,12 +9031,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -8982,7 +9051,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8997,7 +9066,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9015,7 +9084,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9027,7 +9096,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>30</v>
@@ -9048,7 +9117,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9060,10 +9129,10 @@
         <v>281</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9081,7 +9150,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9096,7 +9165,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9114,7 +9183,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9126,7 +9195,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>92</v>
@@ -9162,7 +9231,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9174,15 +9243,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9197,7 +9266,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9219,7 +9288,7 @@
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9234,7 +9303,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9249,7 +9318,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9267,7 +9336,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9279,10 +9348,10 @@
         <v>231</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9300,7 +9369,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9315,7 +9384,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9333,7 +9402,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9345,7 +9414,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>279</v>
@@ -9366,7 +9435,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9378,10 +9447,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9414,7 +9483,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9429,12 +9498,12 @@
         <v>78</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9449,7 +9518,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9461,7 +9530,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>66</v>
@@ -9482,7 +9551,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9530,7 +9599,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9542,15 +9611,15 @@
         <v>83</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9565,7 +9634,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9574,17 +9643,19 @@
         <v>83</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
-      <c r="M254" s="7"/>
+      <c t="s" r="M254" s="7">
+        <v>345</v>
+      </c>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
@@ -9598,13 +9669,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>83</v>
@@ -9613,7 +9684,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9627,11 +9698,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C256" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9640,13 +9711,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9660,26 +9731,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C257" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9712,7 +9783,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9724,10 +9795,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9747,7 +9818,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9759,14 +9830,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>110</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
@@ -9780,7 +9853,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -9795,7 +9868,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9813,7 +9886,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -9825,7 +9898,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>67</v>
@@ -9846,7 +9919,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9855,13 +9928,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>277</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9879,22 +9952,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9927,7 +10000,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9936,10 +10009,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>192</v>
@@ -9947,7 +10020,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9962,27 +10035,27 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -9997,7 +10070,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10009,14 +10082,16 @@
         <v>83</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
-      <c r="M268" s="7"/>
+      <c t="s" r="M268" s="7">
+        <v>50</v>
+      </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
@@ -10030,7 +10105,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10042,14 +10117,18 @@
         <v>39</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>260</v>
-      </c>
-      <c r="K269" s="7"/>
+        <v>261</v>
+      </c>
+      <c t="s" r="K269" s="7">
+        <v>41</v>
+      </c>
       <c r="L269" s="7"/>
-      <c r="M269" s="7"/>
+      <c t="s" r="M269" s="7">
+        <v>305</v>
+      </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c t="s" r="A270" s="6">
@@ -10063,7 +10142,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10078,7 +10157,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10096,7 +10175,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10111,7 +10190,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10129,7 +10208,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10141,10 +10220,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10177,7 +10256,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10189,7 +10268,7 @@
         <v>188</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>80</v>
@@ -10197,7 +10276,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10212,7 +10291,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10224,14 +10303,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
-      <c r="M275" s="7"/>
+      <c t="s" r="M275" s="7">
+        <v>362</v>
+      </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
       <c t="s" r="A276" s="6">
@@ -10245,7 +10326,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10254,10 +10335,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>222</v>
@@ -10278,22 +10359,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10326,7 +10407,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10335,18 +10416,18 @@
         <v>39</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10361,13 +10442,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>39</v>
@@ -10381,7 +10462,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10396,7 +10477,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10415,7 +10496,9 @@
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
-      <c r="M281" s="7"/>
+      <c t="s" r="M281" s="7">
+        <v>259</v>
+      </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
       <c t="s" r="A282" s="6">
@@ -10429,7 +10512,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10444,11 +10527,15 @@
         <v>110</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>171</v>
-      </c>
-      <c r="K282" s="7"/>
+        <v>371</v>
+      </c>
+      <c t="s" r="K282" s="7">
+        <v>52</v>
+      </c>
       <c r="L282" s="7"/>
-      <c r="M282" s="7"/>
+      <c t="s" r="M282" s="7">
+        <v>213</v>
+      </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
       <c t="s" r="A283" s="6">
@@ -10462,7 +10549,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10471,7 +10558,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>89</v>
@@ -10495,22 +10582,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10528,7 +10615,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10537,10 +10624,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>40</v>
@@ -10576,7 +10663,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10591,14 +10678,14 @@
         <v>191</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="K287" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10613,7 +10700,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10622,7 +10709,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>182</v>
@@ -10631,11 +10718,11 @@
         <v>52</v>
       </c>
       <c t="s" r="K288" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10650,29 +10737,29 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10687,7 +10774,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10696,7 +10783,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I290" s="7">
         <v>45</v>
@@ -10720,22 +10807,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10768,7 +10855,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10783,12 +10870,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10803,7 +10890,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10818,12 +10905,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10838,7 +10925,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10847,10 +10934,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>73</v>
@@ -10871,19 +10958,19 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>103</v>
@@ -10919,7 +11006,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10934,12 +11021,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>96</v>
+        <v>380</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10954,7 +11041,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10987,7 +11074,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11002,11 +11089,15 @@
         <v>52</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>373</v>
-      </c>
-      <c r="K300" s="7"/>
+        <v>381</v>
+      </c>
+      <c t="s" r="K300" s="7">
+        <v>298</v>
+      </c>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>226</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -11020,7 +11111,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11032,10 +11123,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11053,7 +11144,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11062,13 +11153,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>277</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11086,19 +11177,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>72</v>
@@ -11119,7 +11210,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11134,7 +11225,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11167,7 +11258,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11176,18 +11267,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11202,19 +11293,19 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>223</v>
@@ -11222,7 +11313,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11237,7 +11328,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11249,17 +11340,17 @@
         <v>39</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="K308" s="7">
         <v>194</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11274,7 +11365,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11286,7 +11377,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>52</v>
@@ -11296,7 +11387,7 @@
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>246</v>
+        <v>391</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11311,7 +11402,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11323,10 +11414,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="K310" s="7">
         <v>29</v>
@@ -11348,7 +11439,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11360,10 +11451,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11396,7 +11487,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11408,15 +11499,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11431,7 +11522,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11440,10 +11531,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>49</v>
@@ -11451,7 +11542,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11466,19 +11557,19 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>61</v>
@@ -11486,7 +11577,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11501,7 +11592,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11513,17 +11604,17 @@
         <v>91</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>42</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>276</v>
+        <v>396</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11538,7 +11629,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11553,14 +11644,14 @@
         <v>85</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11575,7 +11666,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11584,13 +11675,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11608,13 +11699,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>25</v>
@@ -11641,7 +11732,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11650,13 +11741,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11674,22 +11765,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11722,7 +11813,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11734,15 +11825,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11757,7 +11848,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11766,13 +11857,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11792,19 +11883,19 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>44</v>
@@ -11825,7 +11916,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11837,10 +11928,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11873,7 +11964,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11882,18 +11973,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11908,29 +11999,29 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11945,7 +12036,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11957,17 +12048,17 @@
         <v>231</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>82</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>196</v>
+        <v>404</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11982,7 +12073,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11997,10 +12088,10 @@
         <v>84</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
@@ -12019,7 +12110,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12031,10 +12122,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>171</v>
+        <v>371</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12052,7 +12143,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12064,10 +12155,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>172</v>
+        <v>405</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12085,7 +12176,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12100,7 +12191,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12118,7 +12209,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12130,10 +12221,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12151,7 +12242,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12163,10 +12254,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12199,7 +12290,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12214,12 +12305,12 @@
         <v>62</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12234,7 +12325,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12246,15 +12337,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12269,7 +12360,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12284,7 +12375,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12302,7 +12393,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12339,7 +12430,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12348,13 +12439,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12372,13 +12463,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>25</v>
@@ -12420,7 +12511,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12432,7 +12523,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>110</v>
@@ -12455,7 +12546,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12467,7 +12558,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>277</v>
@@ -12488,7 +12579,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12503,7 +12594,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12521,7 +12612,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12533,10 +12624,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12569,13 +12660,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>25</v>
@@ -12589,7 +12680,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>225</v>
+        <v>42</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12604,7 +12695,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12616,7 +12707,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>66</v>
@@ -12637,7 +12728,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12649,10 +12740,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12670,7 +12761,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12679,13 +12770,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12703,13 +12794,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>25</v>
@@ -12751,7 +12842,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12766,12 +12857,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12786,7 +12877,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12798,14 +12889,16 @@
         <v>39</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>52</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
+      <c t="s" r="M357" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
       <c t="s" r="A358" s="6">
@@ -12819,7 +12912,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12831,7 +12924,7 @@
         <v>281</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>66</v>
@@ -12852,7 +12945,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12864,10 +12957,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12885,7 +12978,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12894,13 +12987,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12918,22 +13011,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12966,7 +13059,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12978,15 +13071,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13001,7 +13094,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13013,15 +13106,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13036,7 +13129,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13045,13 +13138,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13069,22 +13162,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13102,7 +13195,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13111,13 +13204,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13135,22 +13228,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13183,7 +13276,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13192,18 +13285,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13218,13 +13311,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>105</v>
@@ -13233,11 +13326,13 @@
         <v>18</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>246</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
@@ -13251,7 +13346,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13260,7 +13355,7 @@
         <v>105</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>41</v>
@@ -13284,22 +13379,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13317,7 +13412,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13326,13 +13421,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>175</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13350,22 +13445,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13398,7 +13493,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13417,7 +13512,9 @@
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
-      <c r="M377" s="7"/>
+      <c t="s" r="M377" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
       <c t="s" r="A378" s="6">
@@ -13431,7 +13528,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13443,7 +13540,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>66</v>
@@ -13464,7 +13561,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13476,10 +13573,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13497,7 +13594,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13512,7 +13609,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13530,7 +13627,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13545,7 +13642,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13578,7 +13675,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13598,7 +13695,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>417</v>
+        <v>428</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13613,7 +13710,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13628,12 +13725,12 @@
         <v>49</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13648,7 +13745,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13657,10 +13754,10 @@
         <v>83</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>67</v>
@@ -13681,13 +13778,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>25</v>
@@ -13696,7 +13793,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13714,7 +13811,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13726,10 +13823,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13747,7 +13844,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13759,7 +13856,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>191</v>
@@ -13795,7 +13892,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13815,7 +13912,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13830,7 +13927,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13863,7 +13960,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13878,7 +13975,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13896,7 +13993,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13911,7 +14008,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13929,7 +14026,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13944,7 +14041,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13977,7 +14074,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13989,15 +14086,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14012,7 +14109,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14024,15 +14121,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14047,7 +14144,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14059,14 +14156,18 @@
         <v>25</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>170</v>
-      </c>
-      <c r="K398" s="7"/>
+        <v>173</v>
+      </c>
+      <c t="s" r="K398" s="7">
+        <v>246</v>
+      </c>
       <c r="L398" s="7"/>
-      <c r="M398" s="7"/>
+      <c t="s" r="M398" s="7">
+        <v>43</v>
+      </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
       <c t="s" r="A399" s="6">
@@ -14080,7 +14181,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14092,10 +14193,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14113,7 +14214,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14125,10 +14226,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14146,7 +14247,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14158,7 +14259,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>22</v>
@@ -14168,7 +14269,7 @@
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>424</v>
+        <v>435</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14194,11 +14295,11 @@
         <v>23</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14207,10 +14308,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>191</v>
@@ -14218,7 +14319,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14248,7 +14349,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14266,7 +14367,7 @@
         <v>187</v>
       </c>
       <c t="s" r="K405" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
@@ -14285,7 +14386,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14297,17 +14398,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="K406" s="7">
         <v>110</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14322,7 +14423,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14334,7 +14435,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>179</v>
@@ -14370,22 +14471,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14405,7 +14506,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14414,13 +14515,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14438,19 +14539,19 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>46</v>
@@ -14471,7 +14572,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14486,7 +14587,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14519,7 +14620,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14531,15 +14632,15 @@
         <v>105</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14554,7 +14655,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14566,7 +14667,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>194</v>
@@ -14574,7 +14675,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14589,7 +14690,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14598,18 +14699,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>434</v>
+        <v>381</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14624,22 +14725,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14657,7 +14758,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14666,10 +14767,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>222</v>
@@ -14690,22 +14791,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14738,7 +14839,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14747,7 +14848,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>23</v>
@@ -14773,13 +14874,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>25</v>
@@ -14788,12 +14889,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -14808,7 +14909,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14823,12 +14924,12 @@
         <v>62</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>439</v>
+        <v>449</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14843,7 +14944,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14855,7 +14956,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>65</v>
@@ -14863,7 +14964,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>440</v>
+        <v>82</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -14878,7 +14979,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14887,13 +14988,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14911,13 +15012,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>25</v>
@@ -14926,7 +15027,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14944,7 +15045,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14959,7 +15060,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14977,7 +15078,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14989,10 +15090,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15025,7 +15126,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15034,18 +15135,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15060,19 +15161,19 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>103</v>
@@ -15108,7 +15209,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15123,7 +15224,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15156,7 +15257,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -15168,10 +15269,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="K435" s="7">
         <v>63</v>
@@ -15193,7 +15294,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15215,7 +15316,7 @@
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15226,11 +15327,11 @@
         <v>8912</v>
       </c>
       <c t="s" r="C437" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15239,13 +15340,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15259,17 +15360,17 @@
         <v>2867</v>
       </c>
       <c t="s" r="C438" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>54</v>
@@ -15278,7 +15379,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15311,7 +15412,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15320,18 +15421,18 @@
         <v>83</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15346,22 +15447,22 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>451</v>
+        <v>322</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15387,20 +15488,20 @@
         <v>13</v>
       </c>
       <c t="s" r="B443" s="7">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c t="s" r="C443" s="7">
         <v>14</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
@@ -15416,7 +15517,7 @@
       </c>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15431,7 +15532,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15443,10 +15544,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15479,7 +15580,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15498,7 +15599,9 @@
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
-      <c r="M446" s="7"/>
+      <c t="s" r="M446" s="7">
+        <v>465</v>
+      </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
       <c t="s" r="A447" s="6">
@@ -15512,7 +15615,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15521,13 +15624,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>451</v>
+        <v>322</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15545,22 +15648,22 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15593,7 +15696,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15608,7 +15711,7 @@
         <v>225</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15626,7 +15729,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -15638,10 +15741,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15659,7 +15762,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -15668,10 +15771,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>106</v>
@@ -15682,7 +15785,7 @@
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c t="s" r="A453" s="9">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -15702,7 +15805,7 @@
     <row r="454" ht="65.25" customHeight="1"/>
     <row r="455" ht="17.25" customHeight="1">
       <c t="s" r="A455" s="10">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -15715,7 +15818,7 @@
       <c r="J455" s="10"/>
       <c r="K455" s="10"/>
       <c t="s" r="L455" s="11">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="M455" s="11"/>
       <c r="N455" s="11"/>

--- a/Data/FlightPlan/FPL_26SEP26.xlsx
+++ b/Data/FlightPlan/FPL_26SEP26.xlsx
@@ -266,553 +266,565 @@
     <t>12:25</t>
   </si>
   <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:47</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>WUX</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>16:43</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
     <t>13:45</t>
   </si>
   <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>12:57</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>13:07</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:06</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:01</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:47</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:23</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>WUX</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>10:48</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:11</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>12:05</t>
+    <t>14:10</t>
   </si>
   <si>
     <t>MNL</t>
@@ -884,6 +896,9 @@
     <t>KUL</t>
   </si>
   <si>
+    <t>14:37</t>
+  </si>
+  <si>
     <t>15:15</t>
   </si>
   <si>
@@ -926,9 +941,6 @@
     <t>13:10</t>
   </si>
   <si>
-    <t>14:10</t>
-  </si>
-  <si>
     <t>16:30</t>
   </si>
   <si>
@@ -965,6 +977,9 @@
     <t>VN-A639</t>
   </si>
   <si>
+    <t>15:07</t>
+  </si>
+  <si>
     <t>20:05</t>
   </si>
   <si>
@@ -977,6 +992,9 @@
     <t>06:25</t>
   </si>
   <si>
+    <t>15:04</t>
+  </si>
+  <si>
     <t>15:20</t>
   </si>
   <si>
@@ -1031,6 +1049,9 @@
     <t>11:26</t>
   </si>
   <si>
+    <t>15:02</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -1046,7 +1067,7 @@
     <t>MFM</t>
   </si>
   <si>
-    <t>14:36</t>
+    <t>15:03</t>
   </si>
   <si>
     <t>16:35</t>
@@ -1091,6 +1112,9 @@
     <t>10:17</t>
   </si>
   <si>
+    <t>14:33</t>
+  </si>
+  <si>
     <t>VN-A653</t>
   </si>
   <si>
@@ -1133,6 +1157,9 @@
     <t>VN-A657</t>
   </si>
   <si>
+    <t>17:00</t>
+  </si>
+  <si>
     <t>20:25</t>
   </si>
   <si>
@@ -1154,12 +1181,6 @@
     <t>11:50</t>
   </si>
   <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
     <t>20:50</t>
   </si>
   <si>
@@ -1184,7 +1205,7 @@
     <t>11:12</t>
   </si>
   <si>
-    <t>13:59</t>
+    <t>14:04</t>
   </si>
   <si>
     <t>VN-A667</t>
@@ -1199,9 +1220,6 @@
     <t>11:11</t>
   </si>
   <si>
-    <t>13:25</t>
-  </si>
-  <si>
     <t>21:45</t>
   </si>
   <si>
@@ -1226,6 +1244,9 @@
     <t>12:32</t>
   </si>
   <si>
+    <t>14:27</t>
+  </si>
+  <si>
     <t>17:05</t>
   </si>
   <si>
@@ -1235,6 +1256,9 @@
     <t>VN-A672</t>
   </si>
   <si>
+    <t>14:34</t>
+  </si>
+  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1283,6 +1307,9 @@
     <t>VN-A677</t>
   </si>
   <si>
+    <t>14:49</t>
+  </si>
+  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1298,6 +1325,9 @@
     <t>08:49</t>
   </si>
   <si>
+    <t>17:08</t>
+  </si>
+  <si>
     <t>20:00</t>
   </si>
   <si>
@@ -1310,12 +1340,18 @@
     <t>11:32</t>
   </si>
   <si>
+    <t>15:09</t>
+  </si>
+  <si>
     <t>VN-A687</t>
   </si>
   <si>
     <t>11:59</t>
   </si>
   <si>
+    <t>14:58</t>
+  </si>
+  <si>
     <t>23:30</t>
   </si>
   <si>
@@ -1331,6 +1367,9 @@
     <t>VN-A693</t>
   </si>
   <si>
+    <t>20:29</t>
+  </si>
+  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1379,6 +1418,9 @@
     <t>VN-A812</t>
   </si>
   <si>
+    <t>13:27</t>
+  </si>
+  <si>
     <t>KJA</t>
   </si>
   <si>
@@ -1406,9 +1448,6 @@
     <t>VN-A817</t>
   </si>
   <si>
-    <t>13:09</t>
-  </si>
-  <si>
     <t>NQZ</t>
   </si>
   <si>
@@ -1424,7 +1463,7 @@
     <t>Total Record(s): 372</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 26, 2026 12:05</t>
+    <t xml:space="preserve">Generated on  Sep 26, 2026 13:24</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5086,7 +5125,9 @@
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
@@ -5109,7 +5150,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>29</v>
@@ -5139,7 +5180,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
@@ -5178,7 +5219,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>93</v>
@@ -5214,7 +5255,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5223,7 +5264,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>92</v>
@@ -5234,7 +5275,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5249,22 +5290,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5282,7 +5323,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5291,7 +5332,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>32</v>
@@ -5315,13 +5356,13 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>39</v>
@@ -5330,7 +5371,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5363,7 +5404,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5383,7 +5424,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5398,7 +5439,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5410,13 +5451,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
@@ -5435,7 +5476,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5468,7 +5509,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5501,7 +5542,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5510,13 +5551,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5549,7 +5590,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5564,7 +5605,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="K123" s="7">
         <v>49</v>
@@ -5586,7 +5627,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5598,14 +5639,16 @@
         <v>39</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
+      <c t="s" r="M124" s="7">
+        <v>228</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c t="s" r="A125" s="6">
@@ -5619,7 +5662,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5628,7 +5671,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="I125" s="7">
         <v>89</v>
@@ -5652,22 +5695,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5700,7 +5743,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5712,7 +5755,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>144</v>
@@ -5720,7 +5763,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5735,7 +5778,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5770,7 +5813,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5779,18 +5822,18 @@
         <v>39</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -5805,13 +5848,13 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>39</v>
@@ -5820,12 +5863,12 @@
         <v>187</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -5840,7 +5883,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5852,7 +5895,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>175</v>
@@ -5873,7 +5916,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5885,10 +5928,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5906,7 +5949,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5915,10 +5958,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>62</v>
@@ -5954,7 +5997,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5966,7 +6009,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>182</v>
@@ -5989,7 +6032,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6022,7 +6065,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6055,7 +6098,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6067,7 +6110,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>72</v>
@@ -6088,7 +6131,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6097,10 +6140,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>167</v>
@@ -6136,7 +6179,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6156,7 +6199,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6171,7 +6214,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6191,7 +6234,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6206,7 +6249,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6218,7 +6261,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>137</v>
@@ -6239,7 +6282,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6254,7 +6297,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6272,7 +6315,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6284,10 +6327,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6305,7 +6348,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6317,10 +6360,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6353,19 +6396,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>114</v>
@@ -6373,7 +6416,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6388,7 +6431,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6400,7 +6443,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>56</v>
@@ -6421,7 +6464,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6436,7 +6479,7 @@
         <v>204</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6454,7 +6497,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6463,10 +6506,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>78</v>
@@ -6502,7 +6545,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6517,12 +6560,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6537,7 +6580,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6549,14 +6592,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>44</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c t="s" r="M155" s="7">
+        <v>263</v>
+      </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c t="s" r="A156" s="6">
@@ -6570,7 +6615,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6579,13 +6624,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6603,19 +6648,19 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>202</v>
@@ -6636,7 +6681,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6651,7 +6696,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6684,7 +6729,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6693,13 +6738,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6719,13 +6764,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>54</v>
@@ -6734,14 +6779,14 @@
         <v>41</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c t="s" r="K161" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6756,7 +6801,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6765,13 +6810,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6789,13 +6834,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>25</v>
@@ -6822,7 +6867,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6831,13 +6876,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6855,22 +6900,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6903,7 +6948,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6938,7 +6983,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6953,12 +6998,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6973,7 +7018,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6988,7 +7033,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="K169" s="7">
         <v>148</v>
@@ -7010,7 +7055,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7022,13 +7067,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>52</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
@@ -7047,7 +7092,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7059,10 +7104,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7080,7 +7125,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7092,10 +7137,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7128,7 +7173,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7137,7 +7182,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I174" s="7">
         <v>144</v>
@@ -7163,13 +7208,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>91</v>
@@ -7178,12 +7223,12 @@
         <v>122</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7198,7 +7243,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7207,10 +7252,10 @@
         <v>91</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>41</v>
@@ -7218,7 +7263,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7233,13 +7278,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>39</v>
@@ -7266,7 +7311,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7278,7 +7323,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>189</v>
@@ -7299,7 +7344,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7347,7 +7392,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7356,10 +7401,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>74</v>
@@ -7367,7 +7412,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7382,19 +7427,19 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>27</v>
@@ -7402,7 +7447,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7417,7 +7462,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7426,7 +7471,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>40</v>
@@ -7452,13 +7497,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>25</v>
@@ -7471,7 +7516,9 @@
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
+      <c t="s" r="M184" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
@@ -7485,7 +7532,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7497,7 +7544,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>100</v>
@@ -7518,7 +7565,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7533,7 +7580,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7566,7 +7613,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7578,15 +7625,15 @@
         <v>83</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7601,7 +7648,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7616,12 +7663,12 @@
         <v>78</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7636,7 +7683,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7648,17 +7695,17 @@
         <v>112</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c t="s" r="K190" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7673,7 +7720,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7688,10 +7735,10 @@
         <v>42</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c t="s" r="K191" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
@@ -7710,7 +7757,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7719,13 +7766,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>183</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7743,22 +7790,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7791,7 +7838,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7800,13 +7847,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7826,22 +7873,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7861,7 +7908,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7873,7 +7920,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>137</v>
@@ -7894,7 +7941,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7906,10 +7953,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7927,7 +7974,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7939,7 +7986,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>117</v>
@@ -7960,7 +8007,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7972,7 +8019,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>168</v>
@@ -8008,7 +8055,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8028,7 +8075,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8043,7 +8090,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8055,7 +8102,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>172</v>
@@ -8063,7 +8110,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8078,7 +8125,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8090,7 +8137,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>196</v>
@@ -8113,7 +8160,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8125,13 +8172,13 @@
         <v>39</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>173</v>
       </c>
       <c t="s" r="K205" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
@@ -8150,7 +8197,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8159,7 +8206,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>89</v>
@@ -8183,13 +8230,13 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>39</v>
@@ -8216,7 +8263,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8225,13 +8272,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8249,22 +8296,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8297,7 +8344,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8309,14 +8356,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>135</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
-      <c r="M211" s="7"/>
+      <c t="s" r="M211" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
       <c t="s" r="A212" s="6">
@@ -8330,7 +8379,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8363,7 +8412,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8378,7 +8427,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8396,7 +8445,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8408,10 +8457,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8444,7 +8493,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8456,7 +8505,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>78</v>
@@ -8479,7 +8528,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8488,7 +8537,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>182</v>
@@ -8514,19 +8563,19 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>88</v>
@@ -8536,7 +8585,7 @@
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>98</v>
+        <v>327</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8551,7 +8600,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8563,17 +8612,17 @@
         <v>165</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>53</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8588,7 +8637,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8600,7 +8649,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>116</v>
@@ -8629,14 +8678,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B222" s="7">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8648,17 +8697,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="K222" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8673,7 +8722,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8685,7 +8734,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>151</v>
@@ -8693,7 +8742,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8708,7 +8757,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8723,7 +8772,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="K224" s="7">
         <v>88</v>
@@ -8745,7 +8794,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8757,10 +8806,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c t="s" r="K225" s="7">
         <v>67</v>
@@ -8797,7 +8846,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8832,7 +8881,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8852,7 +8901,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8867,7 +8916,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8882,12 +8931,12 @@
         <v>207</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8902,7 +8951,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8917,7 +8966,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8935,7 +8984,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8950,7 +8999,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8968,7 +9017,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8980,10 +9029,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9016,13 +9065,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>39</v>
@@ -9051,7 +9100,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9066,7 +9115,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9084,7 +9133,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9096,7 +9145,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>30</v>
@@ -9117,7 +9166,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9126,13 +9175,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9150,13 +9199,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>39</v>
@@ -9183,7 +9232,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9231,7 +9280,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9243,15 +9292,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9266,7 +9315,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9288,7 +9337,7 @@
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9303,7 +9352,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9318,11 +9367,13 @@
         <v>41</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c r="M243" s="7"/>
+      <c t="s" r="M243" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c t="s" r="A244" s="6">
@@ -9336,7 +9387,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9345,13 +9396,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>137</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9369,13 +9420,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>39</v>
@@ -9384,7 +9435,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9402,7 +9453,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9414,10 +9465,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9435,7 +9486,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9447,7 +9498,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>129</v>
@@ -9483,7 +9534,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9498,7 +9549,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9518,7 +9569,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9551,7 +9602,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9599,7 +9650,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9619,7 +9670,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9634,7 +9685,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9643,7 +9694,7 @@
         <v>83</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>196</v>
@@ -9654,7 +9705,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9669,13 +9720,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>83</v>
@@ -9684,7 +9735,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9702,7 +9753,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9711,13 +9762,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="I256" s="7">
         <v>205</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9735,22 +9786,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9783,7 +9834,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9795,10 +9846,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9818,7 +9869,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9830,7 +9881,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>110</v>
@@ -9838,7 +9889,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9853,7 +9904,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -9862,13 +9913,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9886,19 +9937,19 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>67</v>
@@ -9919,7 +9970,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -9928,13 +9979,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9952,22 +10003,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10000,7 +10051,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10012,7 +10063,7 @@
         <v>201</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>192</v>
@@ -10020,7 +10071,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10035,7 +10086,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10050,12 +10101,12 @@
         <v>169</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10070,7 +10121,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10082,10 +10133,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10105,7 +10156,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10117,17 +10168,17 @@
         <v>39</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="K269" s="7">
         <v>41</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>305</v>
+        <v>367</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10142,7 +10193,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10175,7 +10226,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10190,7 +10241,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10208,7 +10259,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10220,10 +10271,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10256,7 +10307,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10276,7 +10327,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10291,7 +10342,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10303,7 +10354,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>125</v>
@@ -10311,7 +10362,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10326,7 +10377,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10335,13 +10386,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10359,22 +10410,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10407,7 +10458,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10416,18 +10467,18 @@
         <v>39</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10442,13 +10493,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>39</v>
@@ -10462,7 +10513,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10477,7 +10528,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10497,7 +10548,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>259</v>
+        <v>110</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10512,7 +10563,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10527,14 +10578,14 @@
         <v>110</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c t="s" r="K282" s="7">
         <v>52</v>
       </c>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10549,7 +10600,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10558,7 +10609,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>89</v>
@@ -10566,9 +10617,13 @@
       <c t="s" r="J283" s="7">
         <v>100</v>
       </c>
-      <c r="K283" s="7"/>
+      <c t="s" r="K283" s="7">
+        <v>237</v>
+      </c>
       <c r="L283" s="7"/>
-      <c r="M283" s="7"/>
+      <c t="s" r="M283" s="7">
+        <v>200</v>
+      </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
       <c t="s" r="A284" s="6">
@@ -10582,13 +10637,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>39</v>
@@ -10597,7 +10652,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10615,7 +10670,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10624,10 +10679,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>40</v>
@@ -10663,7 +10718,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10681,7 +10736,7 @@
         <v>144</v>
       </c>
       <c t="s" r="K287" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
@@ -10700,7 +10755,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10709,7 +10764,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>182</v>
@@ -10718,11 +10773,11 @@
         <v>52</v>
       </c>
       <c t="s" r="K288" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>291</v>
+        <v>328</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10737,13 +10792,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>25</v>
@@ -10752,14 +10807,14 @@
         <v>173</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>284</v>
+        <v>382</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10774,7 +10829,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10807,7 +10862,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10819,10 +10874,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10855,7 +10910,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10870,12 +10925,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10890,7 +10945,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10910,7 +10965,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10925,7 +10980,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10934,7 +10989,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>138</v>
@@ -10958,19 +11013,19 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>103</v>
@@ -11006,7 +11061,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11015,18 +11070,18 @@
         <v>83</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11041,13 +11096,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>83</v>
@@ -11060,7 +11115,9 @@
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
-      <c r="M299" s="7"/>
+      <c t="s" r="M299" s="7">
+        <v>52</v>
+      </c>
     </row>
     <row r="300" ht="15" customHeight="1">
       <c t="s" r="A300" s="6">
@@ -11074,7 +11131,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11089,14 +11146,14 @@
         <v>52</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>381</v>
+        <v>136</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11111,7 +11168,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11123,7 +11180,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>382</v>
@@ -11144,7 +11201,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11153,13 +11210,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11177,19 +11234,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>72</v>
@@ -11210,7 +11267,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11258,7 +11315,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11267,10 +11324,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>166</v>
@@ -11278,7 +11335,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11293,13 +11350,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>25</v>
@@ -11308,12 +11365,12 @@
         <v>168</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11328,7 +11385,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11350,7 +11407,7 @@
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11365,7 +11422,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11387,7 +11444,7 @@
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11402,7 +11459,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11414,7 +11471,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>199</v>
@@ -11439,7 +11496,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11487,7 +11544,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11499,15 +11556,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11522,7 +11579,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11531,10 +11588,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>49</v>
@@ -11542,7 +11599,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11557,19 +11614,19 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>61</v>
@@ -11577,7 +11634,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11592,7 +11649,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11604,17 +11661,17 @@
         <v>91</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>42</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>396</v>
+        <v>249</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11629,7 +11686,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11641,17 +11698,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>198</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>261</v>
+        <v>160</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>198</v>
+        <v>237</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11666,7 +11723,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11675,10 +11732,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>126</v>
@@ -11699,19 +11756,19 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>56</v>
@@ -11732,7 +11789,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11741,13 +11798,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11765,22 +11822,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11813,7 +11870,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11825,15 +11882,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11848,7 +11905,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11860,10 +11917,10 @@
         <v>159</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11883,7 +11940,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11895,7 +11952,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>44</v>
@@ -11916,7 +11973,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11931,7 +11988,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11964,7 +12021,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11976,7 +12033,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>120</v>
@@ -11999,7 +12056,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12017,11 +12074,11 @@
         <v>172</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12036,7 +12093,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12045,20 +12102,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>82</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12073,13 +12130,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>25</v>
@@ -12088,14 +12145,14 @@
         <v>84</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c t="s" r="K331" s="7">
         <v>157</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>86</v>
+        <v>411</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12110,7 +12167,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12122,10 +12179,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12143,7 +12200,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12155,10 +12212,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12176,7 +12233,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12191,7 +12248,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12209,7 +12266,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12221,10 +12278,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12242,7 +12299,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12257,7 +12314,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12290,7 +12347,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12305,12 +12362,12 @@
         <v>62</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12325,7 +12382,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12337,15 +12394,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12360,7 +12417,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12375,11 +12432,13 @@
         <v>63</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
-      <c r="M340" s="7"/>
+      <c t="s" r="M340" s="7">
+        <v>415</v>
+      </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
       <c t="s" r="A341" s="6">
@@ -12393,7 +12452,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12430,7 +12489,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12439,13 +12498,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12463,19 +12522,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>70</v>
@@ -12511,7 +12570,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12546,7 +12605,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12558,10 +12617,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12579,7 +12638,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12594,7 +12653,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12612,7 +12671,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12624,7 +12683,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>132</v>
@@ -12660,13 +12719,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>25</v>
@@ -12695,7 +12754,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12707,7 +12766,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>66</v>
@@ -12728,7 +12787,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12761,7 +12820,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12770,10 +12829,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>129</v>
@@ -12794,13 +12853,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>25</v>
@@ -12842,7 +12901,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12862,7 +12921,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12877,7 +12936,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12889,7 +12948,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>52</v>
@@ -12912,7 +12971,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12921,10 +12980,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>66</v>
@@ -12945,13 +13004,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>39</v>
@@ -12978,7 +13037,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12987,13 +13046,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13011,22 +13070,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13059,7 +13118,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13071,15 +13130,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13094,7 +13153,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13109,7 +13168,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13129,7 +13188,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13138,10 +13197,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>382</v>
@@ -13162,13 +13221,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>39</v>
@@ -13177,7 +13236,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13195,7 +13254,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13204,13 +13263,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13228,22 +13287,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>39</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13276,7 +13335,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13291,7 +13350,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13311,7 +13370,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13331,7 +13390,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13346,7 +13405,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13365,7 +13424,9 @@
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
+      <c t="s" r="M372" s="7">
+        <v>432</v>
+      </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c t="s" r="A373" s="6">
@@ -13379,7 +13440,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13391,7 +13452,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>200</v>
@@ -13412,7 +13473,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13427,7 +13488,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13445,7 +13506,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13457,10 +13518,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13493,7 +13554,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13528,7 +13589,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13540,7 +13601,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>66</v>
@@ -13561,7 +13622,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13576,7 +13637,7 @@
         <v>382</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13594,7 +13655,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13609,7 +13670,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13627,7 +13688,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13642,7 +13703,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13675,7 +13736,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13695,7 +13756,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13710,7 +13771,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13745,7 +13806,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13754,17 +13815,19 @@
         <v>83</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>67</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
-      <c r="M385" s="7"/>
+      <c t="s" r="M385" s="7">
+        <v>438</v>
+      </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
@@ -13778,13 +13841,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>25</v>
@@ -13811,7 +13874,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13823,7 +13886,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>202</v>
@@ -13844,7 +13907,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13856,7 +13919,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>191</v>
@@ -13892,7 +13955,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13912,7 +13975,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13927,7 +13990,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13942,11 +14005,13 @@
         <v>110</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
-      <c r="M391" s="7"/>
+      <c t="s" r="M391" s="7">
+        <v>443</v>
+      </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
       <c t="s" r="A392" s="6">
@@ -13960,7 +14025,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13993,7 +14058,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14005,10 +14070,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14026,7 +14091,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14041,7 +14106,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14074,7 +14139,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14109,7 +14174,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14124,12 +14189,12 @@
         <v>142</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14144,7 +14209,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14156,17 +14221,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>173</v>
       </c>
       <c t="s" r="K398" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>43</v>
+        <v>446</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14181,7 +14246,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14193,10 +14258,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14214,7 +14279,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14226,10 +14291,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14247,7 +14312,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14259,7 +14324,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>22</v>
@@ -14269,7 +14334,7 @@
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14295,11 +14360,11 @@
         <v>23</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14308,10 +14373,10 @@
         <v>39</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>191</v>
@@ -14319,7 +14384,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14349,7 +14414,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14386,7 +14451,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14398,17 +14463,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="K406" s="7">
         <v>110</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>318</v>
+        <v>452</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14423,7 +14488,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14435,7 +14500,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>179</v>
@@ -14471,13 +14536,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>39</v>
@@ -14486,7 +14551,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14506,7 +14571,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14515,7 +14580,7 @@
         <v>39</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>52</v>
@@ -14539,13 +14604,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>39</v>
@@ -14572,7 +14637,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14620,7 +14685,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14632,7 +14697,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>120</v>
@@ -14640,7 +14705,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14655,7 +14720,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14675,7 +14740,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>444</v>
+        <v>457</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14690,7 +14755,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14699,10 +14764,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>173</v>
@@ -14710,7 +14775,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>381</v>
+        <v>136</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14725,19 +14790,19 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>153</v>
@@ -14758,7 +14823,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14767,13 +14832,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14791,22 +14856,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14839,7 +14904,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14848,7 +14913,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>23</v>
@@ -14874,13 +14939,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>25</v>
@@ -14894,7 +14959,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>448</v>
+        <v>461</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -14909,7 +14974,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14918,18 +14983,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I423" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14944,19 +15009,19 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>65</v>
@@ -14979,7 +15044,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14988,17 +15053,19 @@
         <v>25</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
-      <c r="M425" s="7"/>
+      <c t="s" r="M425" s="7">
+        <v>85</v>
+      </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
       <c t="s" r="A426" s="6">
@@ -15012,13 +15079,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>25</v>
@@ -15027,7 +15094,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -15045,7 +15112,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15060,7 +15127,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15078,7 +15145,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -15090,10 +15157,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15126,7 +15193,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15135,18 +15202,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15161,19 +15228,19 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>103</v>
@@ -15209,7 +15276,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15224,7 +15291,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15257,7 +15324,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -15272,14 +15339,14 @@
         <v>150</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="K435" s="7">
         <v>63</v>
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>110</v>
+        <v>469</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15294,7 +15361,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15306,7 +15373,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>98</v>
@@ -15316,7 +15383,7 @@
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15331,7 +15398,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15340,13 +15407,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15364,13 +15431,13 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>54</v>
@@ -15379,7 +15446,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15412,7 +15479,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15421,18 +15488,18 @@
         <v>83</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>459</v>
+        <v>473</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15447,22 +15514,22 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15488,20 +15555,20 @@
         <v>13</v>
       </c>
       <c t="s" r="B443" s="7">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c t="s" r="C443" s="7">
         <v>14</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
@@ -15517,7 +15584,7 @@
       </c>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15532,7 +15599,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15547,7 +15614,7 @@
         <v>202</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15580,7 +15647,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15595,12 +15662,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>465</v>
+        <v>158</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15615,7 +15682,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15624,13 +15691,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15648,13 +15715,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>83</v>
@@ -15696,7 +15763,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15708,10 +15775,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15729,7 +15796,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -15741,10 +15808,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15762,7 +15829,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -15771,10 +15838,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>106</v>
@@ -15785,7 +15852,7 @@
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c t="s" r="A453" s="9">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -15805,7 +15872,7 @@
     <row r="454" ht="65.25" customHeight="1"/>
     <row r="455" ht="17.25" customHeight="1">
       <c t="s" r="A455" s="10">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -15818,7 +15885,7 @@
       <c r="J455" s="10"/>
       <c r="K455" s="10"/>
       <c t="s" r="L455" s="11">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="M455" s="11"/>
       <c r="N455" s="11"/>

--- a/Data/FlightPlan/FPL_26SEP26.xlsx
+++ b/Data/FlightPlan/FPL_26SEP26.xlsx
@@ -575,6 +575,9 @@
     <t>14:50</t>
   </si>
   <si>
+    <t>16:33</t>
+  </si>
+  <si>
     <t>17:50</t>
   </si>
   <si>
@@ -959,6 +962,9 @@
     <t>14:37</t>
   </si>
   <si>
+    <t>17:42</t>
+  </si>
+  <si>
     <t>VN-A635</t>
   </si>
   <si>
@@ -1022,6 +1028,9 @@
     <t>15:01</t>
   </si>
   <si>
+    <t>17:39</t>
+  </si>
+  <si>
     <t>CAN</t>
   </si>
   <si>
@@ -1058,36 +1067,36 @@
     <t>15:20</t>
   </si>
   <si>
+    <t>771A *</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
-    <t>771A *</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:23</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>14:01</t>
-  </si>
-  <si>
     <t>17:35</t>
   </si>
   <si>
@@ -1178,7 +1187,7 @@
     <t>14:41</t>
   </si>
   <si>
-    <t>16:44</t>
+    <t>16:46</t>
   </si>
   <si>
     <t>21:30</t>
@@ -1325,6 +1334,9 @@
     <t>14:27</t>
   </si>
   <si>
+    <t>16:49</t>
+  </si>
+  <si>
     <t>17:05</t>
   </si>
   <si>
@@ -1334,6 +1346,9 @@
     <t>14:34</t>
   </si>
   <si>
+    <t>17:43</t>
+  </si>
+  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1388,7 +1403,7 @@
     <t>14:49</t>
   </si>
   <si>
-    <t>17:34</t>
+    <t>17:41</t>
   </si>
   <si>
     <t>23:55</t>
@@ -1415,6 +1430,9 @@
     <t>11:32</t>
   </si>
   <si>
+    <t>17:56</t>
+  </si>
+  <si>
     <t>VN-A687</t>
   </si>
   <si>
@@ -1535,6 +1553,9 @@
     <t>NQZ</t>
   </si>
   <si>
+    <t>21:28</t>
+  </si>
+  <si>
     <t>VN-A820</t>
   </si>
   <si>
@@ -1544,7 +1565,7 @@
     <t>Total Record(s): 372</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 26, 2026 15:29</t>
+    <t xml:space="preserve">Generated on  Sep 26, 2026 15:56</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4416,7 +4437,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>45</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4446,14 +4467,14 @@
         <v>55</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="K81" s="7">
         <v>30</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4483,14 +4504,14 @@
         <v>58</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="K82" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4517,17 +4538,17 @@
         <v>94</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="K83" s="7">
         <v>60</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4557,14 +4578,14 @@
         <v>75</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="K84" s="7">
         <v>22</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4594,7 +4615,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4609,12 +4630,12 @@
         <v>77</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4629,7 +4650,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4641,15 +4662,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4664,7 +4685,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4676,7 +4697,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>73</v>
@@ -4712,7 +4733,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4724,7 +4745,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>19</v>
@@ -4747,7 +4768,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4756,18 +4777,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4782,19 +4803,19 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>60</v>
@@ -4830,7 +4851,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4842,15 +4863,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4865,7 +4886,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4877,7 +4898,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>98</v>
@@ -4885,7 +4906,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4900,7 +4921,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4915,12 +4936,12 @@
         <v>158</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4935,7 +4956,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4950,12 +4971,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4970,7 +4991,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4982,10 +5003,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5003,7 +5024,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5012,10 +5033,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>59</v>
@@ -5036,13 +5057,13 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>25</v>
@@ -5051,7 +5072,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5084,7 +5105,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5119,7 +5140,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5138,7 +5159,9 @@
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
+      <c t="s" r="M103" s="7">
+        <v>31</v>
+      </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c t="s" r="A104" s="6">
@@ -5152,7 +5175,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5167,7 +5190,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5185,7 +5208,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5200,7 +5223,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5233,7 +5256,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5245,7 +5268,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>19</v>
@@ -5253,7 +5276,7 @@
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5268,7 +5291,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5277,7 +5300,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>29</v>
@@ -5288,7 +5311,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5303,19 +5326,19 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>34</v>
@@ -5336,7 +5359,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5348,7 +5371,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>96</v>
@@ -5384,7 +5407,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5393,7 +5416,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>95</v>
@@ -5404,7 +5427,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5419,27 +5442,27 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5454,7 +5477,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5463,7 +5486,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>33</v>
@@ -5487,13 +5510,13 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>40</v>
@@ -5502,7 +5525,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5535,7 +5558,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5555,7 +5578,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5570,7 +5593,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5582,13 +5605,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
@@ -5607,7 +5630,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5627,7 +5650,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5642,7 +5665,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5675,7 +5698,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5684,13 +5707,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5723,7 +5746,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5738,7 +5761,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="K123" s="7">
         <v>51</v>
@@ -5760,7 +5783,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5772,15 +5795,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5795,7 +5818,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5804,7 +5827,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I125" s="7">
         <v>118</v>
@@ -5828,22 +5851,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5876,7 +5899,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5888,7 +5911,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>154</v>
@@ -5896,7 +5919,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5911,7 +5934,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5931,7 +5954,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5946,7 +5969,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5955,18 +5978,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -5981,27 +6004,27 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6016,7 +6039,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6031,7 +6054,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6049,7 +6072,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6061,10 +6084,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6082,7 +6105,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6091,10 +6114,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>65</v>
@@ -6130,7 +6153,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6142,10 +6165,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -6165,7 +6188,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6185,7 +6208,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6200,7 +6223,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6233,7 +6256,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6245,7 +6268,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>75</v>
@@ -6266,7 +6289,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6275,10 +6298,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>177</v>
@@ -6314,7 +6337,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6334,7 +6357,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6349,7 +6372,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6369,7 +6392,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6384,7 +6407,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6396,7 +6419,7 @@
         <v>157</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>147</v>
@@ -6404,7 +6427,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6419,7 +6442,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6431,10 +6454,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6452,7 +6475,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6464,10 +6487,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6485,7 +6508,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6497,10 +6520,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6533,19 +6556,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>119</v>
@@ -6553,7 +6576,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6568,7 +6591,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6601,7 +6624,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6613,10 +6636,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6634,7 +6657,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6643,10 +6666,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>81</v>
@@ -6682,7 +6705,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6697,12 +6720,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6717,7 +6740,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6729,7 +6752,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>45</v>
@@ -6737,7 +6760,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6752,7 +6775,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6761,13 +6784,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>163</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6785,22 +6808,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6818,7 +6841,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6833,7 +6856,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6866,7 +6889,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6875,13 +6898,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6901,13 +6924,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>57</v>
@@ -6916,14 +6939,14 @@
         <v>42</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="K161" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6938,7 +6961,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6947,17 +6970,19 @@
         <v>57</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
+      <c t="s" r="M162" s="7">
+        <v>190</v>
+      </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c t="s" r="A163" s="6">
@@ -6971,19 +6996,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>60</v>
@@ -7004,7 +7029,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7013,13 +7038,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7037,22 +7062,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -7085,7 +7110,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7120,7 +7145,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7132,15 +7157,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7155,7 +7180,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7167,10 +7192,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="K169" s="7">
         <v>158</v>
@@ -7192,7 +7217,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7204,13 +7229,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>54</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
@@ -7229,7 +7254,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7241,10 +7266,10 @@
         <v>116</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7262,7 +7287,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7274,10 +7299,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7310,7 +7335,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7319,7 +7344,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I174" s="7">
         <v>154</v>
@@ -7330,7 +7355,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7345,13 +7370,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>94</v>
@@ -7360,12 +7385,12 @@
         <v>132</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7380,7 +7405,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7389,10 +7414,10 @@
         <v>94</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>42</v>
@@ -7400,7 +7425,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7415,13 +7440,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>40</v>
@@ -7450,7 +7475,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7462,10 +7487,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7483,7 +7508,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7531,7 +7556,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7540,10 +7565,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>77</v>
@@ -7551,7 +7576,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7566,19 +7591,19 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>27</v>
@@ -7586,7 +7611,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7601,7 +7626,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7610,7 +7635,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>41</v>
@@ -7636,13 +7661,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>25</v>
@@ -7656,7 +7681,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7671,7 +7696,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7690,7 +7715,9 @@
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
-      <c r="M185" s="7"/>
+      <c t="s" r="M185" s="7">
+        <v>317</v>
+      </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c t="s" r="A186" s="6">
@@ -7704,7 +7731,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7719,7 +7746,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7752,7 +7779,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7764,15 +7791,15 @@
         <v>86</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7787,7 +7814,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7802,12 +7829,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7822,7 +7849,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7834,17 +7861,17 @@
         <v>116</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="K190" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7859,7 +7886,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7877,7 +7904,7 @@
         <v>102</v>
       </c>
       <c t="s" r="K191" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
@@ -7896,7 +7923,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7905,20 +7932,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="K192" s="7">
         <v>55</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7933,19 +7960,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>125</v>
@@ -7981,7 +8008,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7990,13 +8017,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>178</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -8016,22 +8043,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8051,7 +8078,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8063,7 +8090,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>147</v>
@@ -8071,7 +8098,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8086,7 +8113,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8098,10 +8125,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8119,7 +8146,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8131,7 +8158,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>123</v>
@@ -8152,7 +8179,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8164,7 +8191,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>178</v>
@@ -8200,7 +8227,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8212,7 +8239,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>63</v>
@@ -8220,7 +8247,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8235,7 +8262,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8247,7 +8274,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>182</v>
@@ -8255,7 +8282,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8270,7 +8297,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8282,10 +8309,10 @@
         <v>109</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8305,7 +8332,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8317,17 +8344,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>183</v>
       </c>
       <c t="s" r="K205" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8342,7 +8369,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8351,17 +8378,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
-      <c r="M206" s="7"/>
+      <c t="s" r="M206" s="7">
+        <v>339</v>
+      </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
@@ -8375,13 +8404,13 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>40</v>
@@ -8408,7 +8437,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8417,13 +8446,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8441,22 +8470,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8489,7 +8518,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8501,7 +8530,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>145</v>
@@ -8509,7 +8538,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8524,7 +8553,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8543,7 +8572,9 @@
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
-      <c r="M212" s="7"/>
+      <c t="s" r="M212" s="7">
+        <v>47</v>
+      </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c t="s" r="A213" s="6">
@@ -8557,7 +8588,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8572,7 +8603,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8590,7 +8621,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8602,10 +8633,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8638,7 +8669,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8650,7 +8681,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>81</v>
@@ -8673,7 +8704,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8682,13 +8713,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8708,19 +8739,19 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>91</v>
@@ -8730,7 +8761,7 @@
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8745,7 +8776,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8757,17 +8788,17 @@
         <v>175</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>55</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>349</v>
+        <v>31</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8782,7 +8813,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8827,14 +8858,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B222" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8846,17 +8877,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="K222" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8871,7 +8902,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8883,7 +8914,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>161</v>
@@ -8891,7 +8922,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8906,7 +8937,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8921,14 +8952,14 @@
         <v>89</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="K224" s="7">
         <v>91</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8943,7 +8974,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8955,17 +8986,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8995,7 +9026,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9030,7 +9061,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9050,7 +9081,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9065,7 +9096,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9077,15 +9108,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9100,7 +9131,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9115,12 +9146,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9135,7 +9166,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9147,17 +9178,17 @@
         <v>79</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="K231" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9172,7 +9203,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9187,14 +9218,14 @@
         <v>33</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9224,13 +9255,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>40</v>
@@ -9239,7 +9270,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9259,7 +9290,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9274,12 +9305,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9294,7 +9325,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9306,7 +9337,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>30</v>
@@ -9327,7 +9358,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9336,13 +9367,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9360,13 +9391,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>40</v>
@@ -9393,7 +9424,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9441,7 +9472,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9453,15 +9484,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9476,7 +9507,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9498,7 +9529,7 @@
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9513,7 +9544,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9533,7 +9564,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9548,7 +9579,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9557,7 +9588,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>147</v>
@@ -9581,13 +9612,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>40</v>
@@ -9596,7 +9627,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9614,7 +9645,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9626,10 +9657,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9647,7 +9678,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9659,7 +9690,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>139</v>
@@ -9695,7 +9726,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9710,7 +9741,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9730,7 +9761,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9765,7 +9796,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9777,10 +9808,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9813,7 +9844,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9833,7 +9864,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9848,7 +9879,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9857,10 +9888,10 @@
         <v>86</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>187</v>
@@ -9868,7 +9899,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9883,13 +9914,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>86</v>
@@ -9903,7 +9934,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9918,7 +9949,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9927,13 +9958,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9951,22 +9982,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9999,7 +10030,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -10011,15 +10042,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10034,7 +10065,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -10046,7 +10077,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>114</v>
@@ -10054,7 +10085,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10069,7 +10100,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -10078,13 +10109,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10104,13 +10135,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>25</v>
@@ -10119,7 +10150,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10137,7 +10168,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -10146,13 +10177,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10170,22 +10201,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10218,7 +10249,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10227,18 +10258,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10253,13 +10284,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>25</v>
@@ -10268,12 +10299,12 @@
         <v>179</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10288,7 +10319,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10300,10 +10331,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10323,7 +10354,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10335,17 +10366,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="K269" s="7">
         <v>42</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10360,7 +10391,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10380,7 +10411,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10395,7 +10426,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10410,7 +10441,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10428,7 +10459,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10440,10 +10471,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10476,7 +10507,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10485,7 +10516,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>130</v>
@@ -10496,7 +10527,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10511,19 +10542,19 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>187</v>
@@ -10531,7 +10562,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10546,7 +10577,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10555,13 +10586,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10579,22 +10610,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10627,7 +10658,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10636,18 +10667,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10662,19 +10693,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>96</v>
@@ -10682,7 +10713,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10697,7 +10728,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10732,7 +10763,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10747,7 +10778,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c t="s" r="K282" s="7">
         <v>54</v>
@@ -10769,7 +10800,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10778,7 +10809,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>118</v>
@@ -10791,7 +10822,7 @@
       </c>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10806,13 +10837,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>40</v>
@@ -10821,7 +10852,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10839,7 +10870,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10848,10 +10879,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>41</v>
@@ -10887,7 +10918,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10899,13 +10930,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>154</v>
       </c>
       <c t="s" r="K287" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
@@ -10924,7 +10955,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10933,20 +10964,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>54</v>
       </c>
       <c t="s" r="K288" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10961,13 +10992,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>25</v>
@@ -10983,7 +11014,7 @@
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>349</v>
+        <v>362</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10998,7 +11029,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11020,7 +11051,7 @@
       </c>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11035,7 +11066,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11047,17 +11078,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="K291" s="7">
         <v>125</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11087,7 +11118,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11102,12 +11133,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11122,7 +11153,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11142,7 +11173,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11157,7 +11188,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11166,7 +11197,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>148</v>
@@ -11190,19 +11221,19 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>107</v>
@@ -11238,7 +11269,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11247,18 +11278,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11273,13 +11304,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>86</v>
@@ -11308,7 +11339,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11326,11 +11357,11 @@
         <v>146</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11345,7 +11376,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11357,13 +11388,13 @@
         <v>86</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c t="s" r="K301" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
@@ -11382,7 +11413,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11391,13 +11422,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11415,19 +11446,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>75</v>
@@ -11448,7 +11479,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11460,7 +11491,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>176</v>
@@ -11496,7 +11527,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11505,10 +11536,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>176</v>
@@ -11516,7 +11547,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11531,13 +11562,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>25</v>
@@ -11546,12 +11577,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11566,7 +11597,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11584,11 +11615,11 @@
         <v>158</v>
       </c>
       <c t="s" r="K308" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11603,7 +11634,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11625,7 +11656,7 @@
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11640,7 +11671,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11652,17 +11683,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="K310" s="7">
         <v>29</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11677,7 +11708,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11692,7 +11723,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11725,7 +11756,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11737,15 +11768,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11760,7 +11791,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11769,10 +11800,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>51</v>
@@ -11780,7 +11811,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11795,19 +11826,19 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>64</v>
@@ -11815,7 +11846,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11830,7 +11861,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11842,17 +11873,17 @@
         <v>94</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>43</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11867,7 +11898,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11879,17 +11910,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="K317" s="7">
         <v>170</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11904,7 +11935,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11913,7 +11944,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>185</v>
@@ -11937,19 +11968,19 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>59</v>
@@ -11970,7 +12001,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11979,13 +12010,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -12003,22 +12034,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -12051,7 +12082,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12063,15 +12094,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12086,7 +12117,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12098,10 +12129,10 @@
         <v>169</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -12121,7 +12152,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12133,7 +12164,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>45</v>
@@ -12141,7 +12172,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12156,7 +12187,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12171,7 +12202,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12204,7 +12235,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12216,7 +12247,7 @@
         <v>157</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>130</v>
@@ -12239,7 +12270,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12257,11 +12288,11 @@
         <v>182</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12276,7 +12307,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12285,20 +12316,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>85</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12313,13 +12344,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>25</v>
@@ -12328,14 +12359,14 @@
         <v>87</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="K331" s="7">
         <v>167</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12350,7 +12381,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12362,14 +12393,16 @@
         <v>86</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
-      <c r="M332" s="7"/>
+      <c t="s" r="M332" s="7">
+        <v>441</v>
+      </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
       <c t="s" r="A333" s="6">
@@ -12383,7 +12416,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12395,10 +12428,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12416,7 +12449,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12431,7 +12464,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12449,7 +12482,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12464,7 +12497,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12482,7 +12515,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12494,10 +12527,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12530,7 +12563,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12545,12 +12578,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12565,7 +12598,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12577,15 +12610,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12600,7 +12633,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12615,12 +12648,12 @@
         <v>66</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12635,7 +12668,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12657,7 +12690,7 @@
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>30</v>
+        <v>445</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12665,14 +12698,14 @@
         <v>13</v>
       </c>
       <c r="B342" s="7">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12681,50 +12714,58 @@
         <v>25</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>417</v>
+        <v>109</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>272</v>
-      </c>
-      <c r="K342" s="7"/>
+        <v>192</v>
+      </c>
+      <c t="s" r="K342" s="7">
+        <v>71</v>
+      </c>
       <c r="L342" s="7"/>
-      <c r="M342" s="7"/>
+      <c t="s" r="M342" s="7">
+        <v>59</v>
+      </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
       <c t="s" r="A343" s="6">
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
+        <v>109</v>
+      </c>
+      <c t="s" r="H343" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I343" s="7">
+        <v>285</v>
+      </c>
+      <c t="s" r="J343" s="7">
+        <v>409</v>
+      </c>
+      <c t="s" r="K343" s="7">
+        <v>48</v>
+      </c>
+      <c r="L343" s="7"/>
+      <c t="s" r="M343" s="7">
         <v>417</v>
       </c>
-      <c t="s" r="H343" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I343" s="7">
-        <v>302</v>
-      </c>
-      <c t="s" r="J343" s="7">
-        <v>73</v>
-      </c>
-      <c r="K343" s="7"/>
-      <c r="L343" s="7"/>
-      <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c r="A344" s="6"/>
@@ -12753,7 +12794,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12788,7 +12829,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12800,15 +12841,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12823,7 +12864,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12838,7 +12879,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12856,7 +12897,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12868,7 +12909,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>142</v>
@@ -12904,13 +12945,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>25</v>
@@ -12939,7 +12980,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12951,7 +12992,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>69</v>
@@ -12959,7 +13000,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12974,7 +13015,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12986,7 +13027,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>120</v>
@@ -13007,7 +13048,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13016,10 +13057,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>139</v>
@@ -13040,13 +13081,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>25</v>
@@ -13088,7 +13129,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13108,7 +13149,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13123,7 +13164,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13135,7 +13176,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>54</v>
@@ -13158,7 +13199,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13167,10 +13208,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>69</v>
@@ -13193,19 +13234,19 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>120</v>
@@ -13226,7 +13267,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13235,13 +13276,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13259,22 +13300,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13307,7 +13348,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13319,15 +13360,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13342,7 +13383,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13357,7 +13398,7 @@
         <v>143</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13377,7 +13418,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13386,18 +13427,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13412,13 +13453,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>40</v>
@@ -13427,7 +13468,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13445,7 +13486,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13454,13 +13495,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13478,22 +13519,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13526,7 +13567,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13541,7 +13582,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13561,7 +13602,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13581,7 +13622,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13596,7 +13637,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13616,7 +13657,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13631,7 +13672,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13646,12 +13687,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13666,7 +13707,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13678,10 +13719,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13699,7 +13740,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13711,10 +13752,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13747,7 +13788,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13782,7 +13823,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13794,7 +13835,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>69</v>
@@ -13817,7 +13858,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13829,7 +13870,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>124</v>
@@ -13850,7 +13891,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13862,10 +13903,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13883,7 +13924,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13898,7 +13939,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13931,7 +13972,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13946,12 +13987,12 @@
         <v>37</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13966,7 +14007,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14001,7 +14042,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14010,18 +14051,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14036,13 +14077,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>25</v>
@@ -14069,7 +14110,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14081,10 +14122,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14102,7 +14143,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14117,7 +14158,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -14150,7 +14191,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14162,7 +14203,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>112</v>
@@ -14170,7 +14211,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14185,7 +14226,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14200,12 +14241,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14220,7 +14261,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14239,7 +14280,9 @@
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
-      <c r="M392" s="7"/>
+      <c t="s" r="M392" s="7">
+        <v>473</v>
+      </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c t="s" r="A393" s="6">
@@ -14253,7 +14296,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14265,10 +14308,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14286,7 +14329,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14301,7 +14344,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14334,7 +14377,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14369,7 +14412,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14384,12 +14427,12 @@
         <v>152</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14404,7 +14447,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14416,17 +14459,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>183</v>
       </c>
       <c t="s" r="K398" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14441,7 +14484,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14453,10 +14496,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14474,7 +14517,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14486,10 +14529,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14507,7 +14550,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14519,7 +14562,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>22</v>
@@ -14529,7 +14572,7 @@
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14555,11 +14598,11 @@
         <v>23</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14568,18 +14611,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14609,7 +14652,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14621,10 +14664,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="K405" s="7">
         <v>179</v>
@@ -14646,7 +14689,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14658,17 +14701,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="K406" s="7">
         <v>114</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14683,7 +14726,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14695,10 +14738,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14731,13 +14774,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>40</v>
@@ -14746,12 +14789,12 @@
         <v>132</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14766,7 +14809,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14775,13 +14818,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14801,13 +14844,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>40</v>
@@ -14834,7 +14877,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14846,7 +14889,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>173</v>
@@ -14882,7 +14925,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14894,7 +14937,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>130</v>
@@ -14902,7 +14945,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14917,7 +14960,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14932,12 +14975,12 @@
         <v>173</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14952,7 +14995,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14961,10 +15004,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>183</v>
@@ -14987,19 +15030,19 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>163</v>
@@ -15007,7 +15050,7 @@
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15022,7 +15065,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15031,13 +15074,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -15055,22 +15098,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -15103,7 +15146,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -15112,7 +15155,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>23</v>
@@ -15138,13 +15181,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>25</v>
@@ -15158,7 +15201,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15173,7 +15216,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -15182,18 +15225,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I423" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15208,19 +15251,19 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>68</v>
@@ -15243,7 +15286,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15252,13 +15295,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15278,13 +15321,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>25</v>
@@ -15293,12 +15336,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15306,14 +15349,14 @@
         <v>13</v>
       </c>
       <c r="B427" s="7">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15322,13 +15365,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>109</v>
+        <v>420</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>191</v>
+        <v>273</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15339,29 +15382,29 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>109</v>
+        <v>420</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>406</v>
+        <v>73</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15394,7 +15437,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15403,18 +15446,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15429,19 +15472,19 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>107</v>
@@ -15477,7 +15520,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15492,12 +15535,12 @@
         <v>43</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15527,7 +15570,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -15542,14 +15585,14 @@
         <v>160</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K435" s="7">
         <v>66</v>
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15564,7 +15607,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15576,7 +15619,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>101</v>
@@ -15586,7 +15629,7 @@
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15601,7 +15644,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15610,13 +15653,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15634,22 +15677,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15682,7 +15725,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15691,18 +15734,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>178</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15717,22 +15760,22 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15758,36 +15801,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B443" s="7">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c t="s" r="C443" s="7">
         <v>14</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="K443" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15802,7 +15845,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15814,10 +15857,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15850,7 +15893,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15865,7 +15908,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15885,7 +15928,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15894,17 +15937,19 @@
         <v>86</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
-      <c r="M447" s="7"/>
+      <c t="s" r="M447" s="7">
+        <v>514</v>
+      </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
       <c t="s" r="A448" s="6">
@@ -15918,13 +15963,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>86</v>
@@ -15966,7 +16011,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -15978,15 +16023,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16001,7 +16046,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -16013,7 +16058,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>121</v>
@@ -16034,7 +16079,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -16043,10 +16088,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>110</v>
@@ -16057,7 +16102,7 @@
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c t="s" r="A453" s="9">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -16077,7 +16122,7 @@
     <row r="454" ht="65.25" customHeight="1"/>
     <row r="455" ht="17.25" customHeight="1">
       <c t="s" r="A455" s="10">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -16090,7 +16135,7 @@
       <c r="J455" s="10"/>
       <c r="K455" s="10"/>
       <c t="s" r="L455" s="11">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="M455" s="11"/>
       <c r="N455" s="11"/>

--- a/Data/FlightPlan/FPL_26SEP26.xlsx
+++ b/Data/FlightPlan/FPL_26SEP26.xlsx
@@ -326,6 +326,9 @@
     <t>17:15</t>
   </si>
   <si>
+    <t>18:10</t>
+  </si>
+  <si>
     <t>23:35</t>
   </si>
   <si>
@@ -371,159 +374,162 @@
     <t>16:10</t>
   </si>
   <si>
-    <t>18:10</t>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>18:26</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>14:25</t>
   </si>
   <si>
     <t>18:40</t>
   </si>
   <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>13:07</t>
-  </si>
-  <si>
-    <t>15:17</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:06</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:01</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -569,6 +575,9 @@
     <t>16:35</t>
   </si>
   <si>
+    <t>17:57</t>
+  </si>
+  <si>
     <t>VN-A542</t>
   </si>
   <si>
@@ -626,6 +635,9 @@
     <t>17:30</t>
   </si>
   <si>
+    <t>22:18</t>
+  </si>
+  <si>
     <t>VN-A544</t>
   </si>
   <si>
@@ -638,9 +650,6 @@
     <t>18:01</t>
   </si>
   <si>
-    <t>18:50</t>
-  </si>
-  <si>
     <t>VN-A547</t>
   </si>
   <si>
@@ -677,6 +686,9 @@
     <t>17:20</t>
   </si>
   <si>
+    <t>17:35</t>
+  </si>
+  <si>
     <t>VDH</t>
   </si>
   <si>
@@ -746,9 +758,6 @@
     <t>10:30</t>
   </si>
   <si>
-    <t>18:26</t>
-  </si>
-  <si>
     <t>01:00</t>
   </si>
   <si>
@@ -770,6 +779,9 @@
     <t>BAX</t>
   </si>
   <si>
+    <t>22:56</t>
+  </si>
+  <si>
     <t>02:05</t>
   </si>
   <si>
@@ -941,6 +953,9 @@
     <t>16:45</t>
   </si>
   <si>
+    <t>18:53</t>
+  </si>
+  <si>
     <t>VN-A634</t>
   </si>
   <si>
@@ -989,6 +1004,9 @@
     <t>VTE</t>
   </si>
   <si>
+    <t>18:37</t>
+  </si>
+  <si>
     <t>19:10</t>
   </si>
   <si>
@@ -1007,6 +1025,9 @@
     <t>16:30</t>
   </si>
   <si>
+    <t>18:23</t>
+  </si>
+  <si>
     <t>19:35</t>
   </si>
   <si>
@@ -1097,9 +1118,6 @@
     <t>17:00</t>
   </si>
   <si>
-    <t>17:35</t>
-  </si>
-  <si>
     <t>22:15</t>
   </si>
   <si>
@@ -1112,6 +1130,9 @@
     <t>15:36</t>
   </si>
   <si>
+    <t>17:41</t>
+  </si>
+  <si>
     <t>21:05</t>
   </si>
   <si>
@@ -1127,6 +1148,9 @@
     <t>15:13</t>
   </si>
   <si>
+    <t>17:28</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -1205,6 +1229,9 @@
     <t>HND</t>
   </si>
   <si>
+    <t>00:24</t>
+  </si>
+  <si>
     <t>02:00</t>
   </si>
   <si>
@@ -1229,6 +1256,9 @@
     <t>15:10</t>
   </si>
   <si>
+    <t>18:16</t>
+  </si>
+  <si>
     <t>FSZ</t>
   </si>
   <si>
@@ -1322,9 +1352,6 @@
     <t>04:05</t>
   </si>
   <si>
-    <t>17:24</t>
-  </si>
-  <si>
     <t>VN-A670</t>
   </si>
   <si>
@@ -1334,7 +1361,7 @@
     <t>14:27</t>
   </si>
   <si>
-    <t>16:49</t>
+    <t>16:58</t>
   </si>
   <si>
     <t>17:05</t>
@@ -1346,7 +1373,7 @@
     <t>14:34</t>
   </si>
   <si>
-    <t>17:43</t>
+    <t>17:49</t>
   </si>
   <si>
     <t>VN-A673</t>
@@ -1367,6 +1394,9 @@
     <t>10:52</t>
   </si>
   <si>
+    <t>18:39</t>
+  </si>
+  <si>
     <t>00:20</t>
   </si>
   <si>
@@ -1385,6 +1415,9 @@
     <t>16:56</t>
   </si>
   <si>
+    <t>19:02</t>
+  </si>
+  <si>
     <t>PVG</t>
   </si>
   <si>
@@ -1403,9 +1436,6 @@
     <t>14:49</t>
   </si>
   <si>
-    <t>17:41</t>
-  </si>
-  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1430,7 +1460,7 @@
     <t>11:32</t>
   </si>
   <si>
-    <t>17:56</t>
+    <t>17:59</t>
   </si>
   <si>
     <t>VN-A687</t>
@@ -1457,9 +1487,6 @@
     <t>VN-A693</t>
   </si>
   <si>
-    <t>20:31</t>
-  </si>
-  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1553,7 +1580,7 @@
     <t>NQZ</t>
   </si>
   <si>
-    <t>21:28</t>
+    <t>21:32</t>
   </si>
   <si>
     <t>VN-A820</t>
@@ -1565,7 +1592,7 @@
     <t>Total Record(s): 372</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 26, 2026 15:56</t>
+    <t xml:space="preserve">Generated on  Sep 26, 2026 16:49</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3110,7 +3137,9 @@
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
+      <c t="s" r="M38" s="7">
+        <v>105</v>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c t="s" r="A39" s="6">
@@ -3136,7 +3165,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>95</v>
@@ -3172,7 +3201,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -3184,10 +3213,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -3207,7 +3236,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3216,10 +3245,10 @@
         <v>94</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J42" s="7">
         <v>27</v>
@@ -3227,7 +3256,7 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c t="s" r="M42" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -3242,13 +3271,13 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>94</v>
@@ -3257,12 +3286,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -3277,7 +3306,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3292,12 +3321,12 @@
         <v>64</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3312,7 +3341,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3321,18 +3350,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3347,22 +3376,22 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c t="s" r="K46" s="7">
         <v>55</v>
@@ -3384,7 +3413,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3421,7 +3450,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3436,7 +3465,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="K48" s="7">
         <v>127</v>
@@ -3523,7 +3552,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3783,7 +3812,9 @@
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
+      <c t="s" r="M59" s="7">
+        <v>149</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c t="s" r="A60" s="6">
@@ -3809,10 +3840,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3842,10 +3873,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3878,7 +3909,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3893,12 +3924,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -3913,7 +3944,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3933,7 +3964,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3948,7 +3979,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3957,18 +3988,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I65" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3983,27 +4014,27 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4018,7 +4049,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4033,7 +4064,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -4066,27 +4097,27 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4101,7 +4132,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4110,18 +4141,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>121</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4136,19 +4167,19 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>123</v>
@@ -4169,7 +4200,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4178,13 +4209,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4217,7 +4248,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4226,20 +4257,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="K74" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4254,19 +4285,19 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>41</v>
@@ -4276,7 +4307,7 @@
       </c>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4291,7 +4322,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4300,20 +4331,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>66</v>
       </c>
       <c t="s" r="K76" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4328,13 +4359,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>25</v>
@@ -4343,14 +4374,14 @@
         <v>52</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="K77" s="7">
         <v>54</v>
       </c>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4365,7 +4396,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4377,17 +4408,17 @@
         <v>86</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>91</v>
       </c>
       <c t="s" r="K78" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>136</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4417,7 +4448,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4429,15 +4460,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4452,7 +4483,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4461,20 +4492,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I81" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="K81" s="7">
         <v>30</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4489,13 +4520,13 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>25</v>
@@ -4504,14 +4535,14 @@
         <v>58</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="K82" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4526,7 +4557,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4538,17 +4569,17 @@
         <v>94</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="K83" s="7">
         <v>60</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4563,7 +4594,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4578,14 +4609,14 @@
         <v>75</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="K84" s="7">
         <v>22</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4615,7 +4646,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4630,12 +4661,12 @@
         <v>77</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4650,7 +4681,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4662,15 +4693,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4685,7 +4716,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4697,14 +4728,16 @@
         <v>40</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>73</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
+      <c t="s" r="M88" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="6"/>
@@ -4733,7 +4766,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4745,7 +4778,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>19</v>
@@ -4768,7 +4801,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4777,18 +4810,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4803,19 +4836,19 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>60</v>
@@ -4851,7 +4884,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4863,15 +4896,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4886,7 +4919,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4898,7 +4931,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>98</v>
@@ -4906,7 +4939,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4921,7 +4954,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4933,15 +4966,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4956,7 +4989,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4971,12 +5004,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4991,7 +5024,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5003,14 +5036,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
-      <c r="M98" s="7"/>
+      <c t="s" r="M98" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c t="s" r="A99" s="6">
@@ -5024,7 +5059,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5033,10 +5068,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>59</v>
@@ -5057,13 +5092,13 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>25</v>
@@ -5072,7 +5107,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5105,7 +5140,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5117,10 +5152,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -5140,7 +5175,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5175,7 +5210,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5190,7 +5225,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5208,7 +5243,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5223,7 +5258,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5256,7 +5291,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5268,7 +5303,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>19</v>
@@ -5276,7 +5311,7 @@
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5291,7 +5326,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5300,7 +5335,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>29</v>
@@ -5311,7 +5346,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5326,19 +5361,19 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>34</v>
@@ -5359,7 +5394,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5371,7 +5406,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>96</v>
@@ -5407,7 +5442,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5416,18 +5451,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5442,27 +5477,27 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5477,7 +5512,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5486,7 +5521,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>33</v>
@@ -5510,13 +5545,13 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>40</v>
@@ -5525,7 +5560,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5558,7 +5593,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5573,12 +5608,12 @@
         <v>130</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5593,7 +5628,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5605,17 +5640,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5630,7 +5665,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5639,18 +5674,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>245</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5665,19 +5700,19 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>126</v>
@@ -5698,7 +5733,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5707,13 +5742,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5746,7 +5781,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5761,14 +5796,14 @@
         <v>80</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c t="s" r="K123" s="7">
         <v>51</v>
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5783,7 +5818,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5795,15 +5830,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5818,7 +5853,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5827,17 +5862,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>139</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
+      <c t="s" r="M125" s="7">
+        <v>256</v>
+      </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c t="s" r="A126" s="6">
@@ -5851,22 +5888,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5899,7 +5936,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5911,15 +5948,15 @@
         <v>86</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5934,7 +5971,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5954,7 +5991,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5969,7 +6006,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5978,18 +6015,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6004,27 +6041,27 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6039,7 +6076,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6051,14 +6088,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>105</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -6072,7 +6111,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6084,10 +6123,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6105,7 +6144,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6114,10 +6153,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>65</v>
@@ -6153,7 +6192,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6165,15 +6204,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6188,7 +6227,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6203,12 +6242,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6223,7 +6262,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6238,7 +6277,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6256,7 +6295,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6268,7 +6307,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>75</v>
@@ -6289,7 +6328,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6298,13 +6337,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6337,7 +6376,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6346,7 +6385,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I142" s="7">
         <v>130</v>
@@ -6357,7 +6396,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6372,19 +6411,19 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>66</v>
@@ -6392,7 +6431,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6407,7 +6446,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6416,10 +6455,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>147</v>
@@ -6427,7 +6466,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6442,22 +6481,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6475,7 +6514,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6487,10 +6526,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6508,7 +6547,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6520,10 +6559,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6556,27 +6595,27 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6591,7 +6630,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6624,7 +6663,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6636,10 +6675,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6657,7 +6696,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6666,10 +6705,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>81</v>
@@ -6705,7 +6744,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6720,12 +6759,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6740,7 +6779,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6752,7 +6791,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>45</v>
@@ -6760,7 +6799,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6775,7 +6814,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6784,13 +6823,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6808,22 +6847,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6841,7 +6880,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6856,7 +6895,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6889,7 +6928,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6898,13 +6937,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6924,13 +6963,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>57</v>
@@ -6939,14 +6978,14 @@
         <v>42</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="K161" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6961,7 +7000,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6970,18 +7009,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6996,19 +7035,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>60</v>
@@ -7029,7 +7068,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7038,13 +7077,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7062,22 +7101,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -7110,7 +7149,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7122,10 +7161,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7145,7 +7184,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7157,15 +7196,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7180,7 +7219,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7189,16 +7228,16 @@
         <v>25</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="K169" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
@@ -7217,29 +7256,29 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>54</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7254,7 +7293,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7263,13 +7302,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7287,22 +7326,22 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7335,7 +7374,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7344,10 +7383,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>65</v>
@@ -7355,7 +7394,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7370,13 +7409,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>94</v>
@@ -7385,12 +7424,12 @@
         <v>132</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7405,7 +7444,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7414,10 +7453,10 @@
         <v>94</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>42</v>
@@ -7425,7 +7464,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7440,13 +7479,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>40</v>
@@ -7475,7 +7514,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7487,14 +7526,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
-      <c r="M178" s="7"/>
+      <c t="s" r="M178" s="7">
+        <v>314</v>
+      </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c t="s" r="A179" s="6">
@@ -7508,7 +7549,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7556,7 +7597,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7565,10 +7606,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>77</v>
@@ -7576,7 +7617,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7591,19 +7632,19 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>27</v>
@@ -7611,7 +7652,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7626,7 +7667,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7635,18 +7676,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7661,13 +7702,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>25</v>
@@ -7681,7 +7722,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7696,7 +7737,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7705,7 +7746,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>102</v>
@@ -7716,7 +7757,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7731,13 +7772,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>25</v>
@@ -7746,7 +7787,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7779,7 +7820,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7791,15 +7832,15 @@
         <v>86</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7814,7 +7855,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7829,12 +7870,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7849,7 +7890,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7858,20 +7899,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c t="s" r="K190" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7886,13 +7927,13 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>25</v>
@@ -7904,7 +7945,7 @@
         <v>102</v>
       </c>
       <c t="s" r="K191" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
@@ -7923,7 +7964,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7932,20 +7973,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="K192" s="7">
         <v>55</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>237</v>
+        <v>331</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7960,19 +8001,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>125</v>
@@ -8008,7 +8049,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8017,13 +8058,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -8043,22 +8084,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8078,7 +8119,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8090,7 +8131,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>147</v>
@@ -8098,7 +8139,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8113,7 +8154,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8125,14 +8166,16 @@
         <v>86</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
-      <c r="M198" s="7"/>
+      <c t="s" r="M198" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c t="s" r="A199" s="6">
@@ -8146,7 +8189,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8158,7 +8201,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>123</v>
@@ -8179,7 +8222,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8191,10 +8234,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -8227,7 +8270,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8236,10 +8279,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>63</v>
@@ -8247,7 +8290,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8262,27 +8305,27 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8297,7 +8340,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8306,18 +8349,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8332,29 +8375,29 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="K205" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8369,7 +8412,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8378,18 +8421,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8404,19 +8447,19 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>48</v>
@@ -8437,7 +8480,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8446,13 +8489,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8470,22 +8513,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8518,7 +8561,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8530,7 +8573,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>145</v>
@@ -8538,7 +8581,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8553,7 +8596,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8588,7 +8631,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8603,7 +8646,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8621,7 +8664,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8633,10 +8676,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8669,7 +8712,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8681,7 +8724,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>81</v>
@@ -8704,7 +8747,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8713,18 +8756,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8739,19 +8782,19 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>91</v>
@@ -8761,7 +8804,7 @@
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8776,7 +8819,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8785,16 +8828,16 @@
         <v>40</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>55</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
@@ -8813,13 +8856,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>40</v>
@@ -8858,14 +8901,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B222" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8877,17 +8920,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="K222" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8902,7 +8945,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8914,15 +8957,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8937,7 +8980,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8952,14 +8995,14 @@
         <v>89</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c t="s" r="K224" s="7">
         <v>91</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8974,7 +9017,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8986,17 +9029,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9026,7 +9069,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9035,10 +9078,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>27</v>
@@ -9061,13 +9104,13 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>40</v>
@@ -9076,12 +9119,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9096,7 +9139,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9108,15 +9151,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9131,7 +9174,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9146,12 +9189,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9166,7 +9209,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9178,17 +9221,17 @@
         <v>79</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="K231" s="7">
-        <v>362</v>
+        <v>225</v>
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9203,7 +9246,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9218,14 +9261,14 @@
         <v>33</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9255,13 +9298,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>40</v>
@@ -9270,12 +9313,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9290,7 +9333,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9305,12 +9348,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9325,7 +9368,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9337,14 +9380,16 @@
         <v>40</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>30</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
-      <c r="M236" s="7"/>
+      <c t="s" r="M236" s="7">
+        <v>373</v>
+      </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c t="s" r="A237" s="6">
@@ -9358,7 +9403,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9367,13 +9412,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9391,13 +9436,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>40</v>
@@ -9406,7 +9451,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9424,7 +9469,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9436,7 +9481,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>95</v>
@@ -9472,7 +9517,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9484,15 +9529,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9507,7 +9552,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9529,7 +9574,7 @@
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9544,7 +9589,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9564,7 +9609,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9579,7 +9624,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9588,7 +9633,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>147</v>
@@ -9598,7 +9643,9 @@
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
-      <c r="M244" s="7"/>
+      <c t="s" r="M244" s="7">
+        <v>379</v>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
@@ -9612,13 +9659,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>40</v>
@@ -9627,7 +9674,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9645,7 +9692,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9657,10 +9704,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9678,7 +9725,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9690,7 +9737,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>139</v>
@@ -9726,7 +9773,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9741,12 +9788,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9761,7 +9808,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9773,7 +9820,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>69</v>
@@ -9796,7 +9843,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9808,10 +9855,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9844,7 +9891,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9856,15 +9903,15 @@
         <v>86</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9879,7 +9926,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9888,18 +9935,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9914,13 +9961,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>86</v>
@@ -9929,12 +9976,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9949,7 +9996,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9958,13 +10005,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9982,22 +10029,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -10030,7 +10077,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -10042,15 +10089,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10065,7 +10112,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -10077,15 +10124,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10100,7 +10147,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -10109,18 +10156,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10135,26 +10182,28 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
-      <c r="M262" s="7"/>
+      <c t="s" r="M262" s="7">
+        <v>379</v>
+      </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c t="s" r="A263" s="6">
@@ -10168,7 +10217,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -10177,17 +10226,21 @@
         <v>25</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>274</v>
-      </c>
-      <c r="K263" s="7"/>
+        <v>278</v>
+      </c>
+      <c t="s" r="K263" s="7">
+        <v>71</v>
+      </c>
       <c r="L263" s="7"/>
-      <c r="M263" s="7"/>
+      <c t="s" r="M263" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
       <c t="s" r="A264" s="6">
@@ -10201,22 +10254,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10249,7 +10302,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10258,18 +10311,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10284,27 +10337,27 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10319,7 +10372,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10331,10 +10384,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10354,7 +10407,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10366,17 +10419,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="K269" s="7">
         <v>42</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10391,7 +10444,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10411,7 +10464,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10426,7 +10479,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10441,7 +10494,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10459,7 +10512,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10471,10 +10524,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10507,7 +10560,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10516,7 +10569,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>130</v>
@@ -10527,7 +10580,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10542,27 +10595,27 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10577,7 +10630,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10586,17 +10639,19 @@
         <v>25</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
-      <c r="M276" s="7"/>
+      <c t="s" r="M276" s="7">
+        <v>406</v>
+      </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
       <c t="s" r="A277" s="6">
@@ -10610,22 +10665,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10658,7 +10713,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10667,18 +10722,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10693,19 +10748,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>96</v>
@@ -10713,7 +10768,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10728,7 +10783,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10748,7 +10803,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10763,7 +10818,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10775,10 +10830,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c t="s" r="K282" s="7">
         <v>54</v>
@@ -10800,7 +10855,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10809,20 +10864,20 @@
         <v>40</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>104</v>
       </c>
       <c t="s" r="K283" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>221</v>
+        <v>415</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10837,13 +10892,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>40</v>
@@ -10852,7 +10907,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10870,7 +10925,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10879,10 +10934,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>41</v>
@@ -10918,7 +10973,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10930,17 +10985,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="K287" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10955,7 +11010,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10964,20 +11019,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>54</v>
       </c>
       <c t="s" r="K288" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10992,29 +11047,29 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>102</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>362</v>
+        <v>225</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11029,7 +11084,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11038,7 +11093,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I290" s="7">
         <v>47</v>
@@ -11047,11 +11102,11 @@
         <v>33</v>
       </c>
       <c t="s" r="K290" s="7">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11066,29 +11121,29 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="K291" s="7">
         <v>125</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11118,7 +11173,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11130,15 +11185,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11153,7 +11208,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11168,12 +11223,12 @@
         <v>96</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11188,7 +11243,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11197,7 +11252,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>148</v>
@@ -11221,22 +11276,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11269,7 +11324,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11278,18 +11333,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11304,13 +11359,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>86</v>
@@ -11319,7 +11374,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11339,7 +11394,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11357,11 +11412,11 @@
         <v>146</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11376,7 +11431,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11388,17 +11443,17 @@
         <v>86</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c t="s" r="K301" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>104</v>
+        <v>225</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11413,7 +11468,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11422,13 +11477,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11446,19 +11501,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>75</v>
@@ -11479,7 +11534,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11491,10 +11546,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11527,7 +11582,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11536,18 +11591,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11562,27 +11617,27 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11597,7 +11652,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11609,17 +11664,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="K308" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11634,7 +11689,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11646,7 +11701,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>54</v>
@@ -11656,7 +11711,7 @@
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11671,7 +11726,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11683,17 +11738,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="K310" s="7">
         <v>29</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11708,7 +11763,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11723,7 +11778,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11756,7 +11811,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11768,15 +11823,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11791,7 +11846,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11800,10 +11855,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>51</v>
@@ -11811,7 +11866,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11826,19 +11881,19 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>64</v>
@@ -11846,7 +11901,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11861,7 +11916,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11873,17 +11928,17 @@
         <v>94</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>43</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11898,7 +11953,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11910,17 +11965,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11935,7 +11990,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11944,17 +11999,19 @@
         <v>25</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>136</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
@@ -11968,19 +12025,19 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>59</v>
@@ -12001,7 +12058,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12010,13 +12067,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -12034,22 +12091,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -12082,7 +12139,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12094,15 +12151,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12117,7 +12174,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12126,13 +12183,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -12152,19 +12209,19 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>45</v>
@@ -12172,7 +12229,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>437</v>
+        <v>225</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12187,7 +12244,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12202,11 +12259,15 @@
         <v>136</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>342</v>
-      </c>
-      <c r="K326" s="7"/>
+        <v>349</v>
+      </c>
+      <c t="s" r="K326" s="7">
+        <v>193</v>
+      </c>
       <c r="L326" s="7"/>
-      <c r="M326" s="7"/>
+      <c t="s" r="M326" s="7">
+        <v>407</v>
+      </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
       <c r="A327" s="6"/>
@@ -12235,7 +12296,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12244,10 +12305,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>130</v>
@@ -12255,7 +12316,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12270,29 +12331,29 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12307,7 +12368,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12316,20 +12377,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>85</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12344,13 +12405,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>25</v>
@@ -12359,14 +12420,14 @@
         <v>87</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12381,7 +12442,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12393,15 +12454,15 @@
         <v>86</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12416,7 +12477,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12428,10 +12489,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12449,7 +12510,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12464,7 +12525,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12482,7 +12543,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12497,7 +12558,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12515,7 +12576,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12527,10 +12588,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12563,7 +12624,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12578,12 +12639,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12598,7 +12659,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12610,15 +12671,15 @@
         <v>25</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12633,7 +12694,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12648,12 +12709,12 @@
         <v>66</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12668,7 +12729,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12690,7 +12751,7 @@
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12705,7 +12766,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12714,13 +12775,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="K342" s="7">
         <v>71</v>
@@ -12742,29 +12803,29 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c t="s" r="K343" s="7">
         <v>48</v>
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12794,7 +12855,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12806,10 +12867,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12829,7 +12890,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12841,15 +12902,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12864,7 +12925,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12879,7 +12940,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12897,7 +12958,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12909,7 +12970,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>142</v>
@@ -12945,13 +13006,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>25</v>
@@ -12960,7 +13021,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12980,7 +13041,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12992,7 +13053,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>69</v>
@@ -13000,7 +13061,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13015,7 +13076,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -13027,14 +13088,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
+      <c t="s" r="M352" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c t="s" r="A353" s="6">
@@ -13048,7 +13111,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13057,10 +13120,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>139</v>
@@ -13081,19 +13144,19 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>23</v>
@@ -13129,7 +13192,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13144,12 +13207,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13164,7 +13227,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13176,7 +13239,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>54</v>
@@ -13199,7 +13262,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13208,10 +13271,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>69</v>
@@ -13234,26 +13297,28 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
-      <c r="M359" s="7"/>
+      <c t="s" r="M359" s="7">
+        <v>461</v>
+      </c>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
@@ -13267,7 +13332,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13276,13 +13341,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13300,22 +13365,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13348,7 +13413,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13360,15 +13425,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13383,7 +13448,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13398,12 +13463,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13418,7 +13483,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13427,18 +13492,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13453,26 +13518,28 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c r="M366" s="7"/>
+      <c t="s" r="M366" s="7">
+        <v>468</v>
+      </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c t="s" r="A367" s="6">
@@ -13486,7 +13553,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13495,13 +13562,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13519,22 +13586,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13567,7 +13634,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13576,18 +13643,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13602,27 +13669,27 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13637,16 +13704,16 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>42</v>
@@ -13657,7 +13724,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13672,13 +13739,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>79</v>
@@ -13687,12 +13754,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>464</v>
+        <v>373</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13707,7 +13774,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13716,13 +13783,13 @@
         <v>79</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13740,22 +13807,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13788,7 +13855,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13803,7 +13870,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13823,7 +13890,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13835,7 +13902,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>69</v>
@@ -13858,7 +13925,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13867,10 +13934,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>124</v>
@@ -13891,22 +13958,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13924,7 +13991,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13939,7 +14006,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13972,7 +14039,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13987,12 +14054,12 @@
         <v>37</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14007,7 +14074,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14022,12 +14089,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14042,7 +14109,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14051,18 +14118,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14077,13 +14144,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>25</v>
@@ -14092,7 +14159,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14110,7 +14177,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14122,10 +14189,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14143,7 +14210,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14158,7 +14225,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -14191,7 +14258,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14203,15 +14270,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14226,7 +14293,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14238,15 +14305,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14261,7 +14328,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14273,7 +14340,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>136</v>
@@ -14281,7 +14348,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14296,7 +14363,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14308,10 +14375,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14329,7 +14396,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14344,7 +14411,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14377,7 +14444,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14389,7 +14456,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>143</v>
@@ -14412,7 +14479,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14424,15 +14491,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14447,7 +14514,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14459,17 +14526,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="K398" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14484,7 +14551,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14496,14 +14563,16 @@
         <v>40</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
-      <c r="M399" s="7"/>
+      <c t="s" r="M399" s="7">
+        <v>105</v>
+      </c>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c t="s" r="A400" s="6">
@@ -14517,7 +14586,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14529,10 +14598,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14550,7 +14619,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14562,7 +14631,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>22</v>
@@ -14572,7 +14641,7 @@
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14598,11 +14667,11 @@
         <v>23</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14611,18 +14680,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14652,7 +14721,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14664,13 +14733,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c t="s" r="K405" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
@@ -14689,7 +14758,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14701,17 +14770,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>482</v>
+        <v>60</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14726,7 +14795,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14738,14 +14807,18 @@
         <v>25</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>197</v>
-      </c>
-      <c r="K407" s="7"/>
+        <v>200</v>
+      </c>
+      <c t="s" r="K407" s="7">
+        <v>73</v>
+      </c>
       <c r="L407" s="7"/>
-      <c r="M407" s="7"/>
+      <c t="s" r="M407" s="7">
+        <v>340</v>
+      </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
       <c r="A408" s="6"/>
@@ -14774,13 +14847,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>40</v>
@@ -14789,12 +14862,12 @@
         <v>132</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14809,7 +14882,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14818,13 +14891,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14844,19 +14917,19 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>48</v>
@@ -14877,7 +14950,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14889,10 +14962,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14925,7 +14998,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14934,10 +15007,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>130</v>
@@ -14945,7 +15018,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14960,27 +15033,27 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14995,7 +15068,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -15004,13 +15077,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -15030,27 +15103,27 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15065,7 +15138,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15074,13 +15147,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -15098,22 +15171,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -15146,7 +15219,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -15155,7 +15228,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="I421" s="7">
         <v>23</v>
@@ -15166,7 +15239,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15181,13 +15254,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>25</v>
@@ -15196,12 +15269,12 @@
         <v>37</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15216,7 +15289,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -15225,18 +15298,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I423" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>493</v>
+        <v>502</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15251,19 +15324,19 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>68</v>
@@ -15286,7 +15359,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15295,13 +15368,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15321,13 +15394,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>25</v>
@@ -15336,12 +15409,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15356,7 +15429,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15365,13 +15438,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15389,19 +15462,19 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>73</v>
@@ -15437,7 +15510,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15446,18 +15519,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15472,22 +15545,22 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -15520,7 +15593,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15535,12 +15608,12 @@
         <v>43</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15570,7 +15643,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -15582,17 +15655,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="K435" s="7">
         <v>66</v>
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15607,7 +15680,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15619,7 +15692,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>101</v>
@@ -15629,7 +15702,7 @@
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>503</v>
+        <v>512</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15644,7 +15717,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15653,13 +15726,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15677,22 +15750,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15725,7 +15798,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15734,18 +15807,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15760,22 +15833,22 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15801,36 +15874,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B443" s="7">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c t="s" r="C443" s="7">
         <v>14</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="K443" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>511</v>
+        <v>520</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15845,7 +15918,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15857,10 +15930,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15893,7 +15966,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -15908,12 +15981,12 @@
         <v>66</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15928,7 +16001,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -15937,18 +16010,18 @@
         <v>86</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15963,13 +16036,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>86</v>
@@ -15978,7 +16051,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -16011,7 +16084,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
@@ -16023,15 +16096,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16046,7 +16119,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -16058,10 +16131,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16079,7 +16152,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -16088,21 +16161,25 @@
         <v>25</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>110</v>
-      </c>
-      <c r="K452" s="7"/>
+        <v>111</v>
+      </c>
+      <c t="s" r="K452" s="7">
+        <v>197</v>
+      </c>
       <c r="L452" s="7"/>
-      <c r="M452" s="7"/>
+      <c t="s" r="M452" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c t="s" r="A453" s="9">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -16122,7 +16199,7 @@
     <row r="454" ht="65.25" customHeight="1"/>
     <row r="455" ht="17.25" customHeight="1">
       <c t="s" r="A455" s="10">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -16135,7 +16212,7 @@
       <c r="J455" s="10"/>
       <c r="K455" s="10"/>
       <c t="s" r="L455" s="11">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="M455" s="11"/>
       <c r="N455" s="11"/>
